--- a/Pension Calculator - Prototype V6.071 Buy Back 3.0.xlsx
+++ b/Pension Calculator - Prototype V6.071 Buy Back 3.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Processing Forms\Pension Applications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9BE7061-AD75-4684-AF29-2150B434B652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D3AB53-5679-41FA-B848-0185A07D3F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="3" xr2:uid="{A7946337-E3BC-4E38-94E2-486A6ADEC80B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A7946337-E3BC-4E38-94E2-486A6ADEC80B}"/>
   </bookViews>
   <sheets>
     <sheet name="Pension Calculator" sheetId="3" r:id="rId1"/>
@@ -2042,24 +2042,12 @@
     <t>Brooklyn A Hoitinga</t>
   </si>
   <si>
-    <t>9. Service Pension</t>
-  </si>
-  <si>
     <t>Louie Anaya</t>
   </si>
   <si>
     <t>301966X65</t>
   </si>
   <si>
-    <t>Charles W. Welch</t>
-  </si>
-  <si>
-    <t>329932X80</t>
-  </si>
-  <si>
-    <t>Xiomara Welch</t>
-  </si>
-  <si>
     <t>Aquilino C. Basa</t>
   </si>
   <si>
@@ -2235,6 +2223,18 @@
   </si>
   <si>
     <t>Andrea Johnson</t>
+  </si>
+  <si>
+    <t>Rigoberto Pimentel</t>
+  </si>
+  <si>
+    <t>Perla S. Pimentel</t>
+  </si>
+  <si>
+    <t>320395X00</t>
+  </si>
+  <si>
+    <t>8. Service Pension Pre-Age 55 &amp; Disability Pension</t>
   </si>
 </sst>
 </file>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="B2" s="539"/>
       <c r="C2" s="548" t="s">
-        <v>432</v>
+        <v>490</v>
       </c>
       <c r="D2" s="548"/>
       <c r="E2" s="548"/>
@@ -5838,7 +5838,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="543" t="s">
-        <v>433</v>
+        <v>492</v>
       </c>
       <c r="J2" s="543"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="B3" s="539"/>
       <c r="C3" s="227">
-        <v>24372</v>
+        <v>23105</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -5858,7 +5858,7 @@
       <c r="B4" s="547"/>
       <c r="C4" s="20" t="str">
         <f>DATEDIF(C3,C5,"y")&amp;"/"&amp;(DATEDIF(C3,C5, "m") - (DATEDIF(C3,C5, "y") * 12))</f>
-        <v>59/8</v>
+        <v>62/3</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="B5" s="539"/>
       <c r="C5" s="227">
-        <v>46174</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="B6" s="539"/>
       <c r="C6" s="543" t="s">
-        <v>434</v>
+        <v>491</v>
       </c>
       <c r="D6" s="543"/>
       <c r="E6" s="543"/>
@@ -5888,11 +5888,11 @@
       <c r="I6" s="539"/>
       <c r="J6" s="12">
         <f>IF(C7=0,"",IF(AND(C3-C7&lt;0,(DATEDIF(C3,C5,"m")-(DATEDIF(C3,C5,"y")*12))-(DATEDIF(C7,C5,"m")-(DATEDIF(C7,C5,"y")*12))=0),DATEDIF(C3,C5,"y")-DATEDIF(C7,C5,"y"),IF(AND(C3-C7&gt;0,(DATEDIF(C7,C5,"m")-(DATEDIF(C7,C5,"y")*12))-(DATEDIF(C3,C5,"m")-(DATEDIF(C3,C5,"y")*12))=0),DATEDIF(C7,C5,"y")-DATEDIF(C3,C5,"y"),IF(C3-C7&lt;0,ROUNDDOWN(YEARFRAC(C3,C7),0),IF(C3-C7&gt;0,ROUNDDOWN(YEARFRAC(C7,C3),0),0)))))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K6" s="1" t="str">
         <f>IF(C7=0,"",IF(J6=0,"No Difference.",IF(C3-C7&lt;0,"Year(s) Younger.", IF(C3-C7&gt;0, "Year(s) Older.","No Difference."))))</f>
-        <v>No Difference.</v>
+        <v>Year(s) Younger.</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="B7" s="539"/>
       <c r="C7" s="227">
-        <v>24432</v>
+        <v>26366</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5912,10 +5912,10 @@
       <c r="B8" s="539"/>
       <c r="C8" s="20" t="str">
         <f>IF(COUNTIF(C7,""),"",DATEDIF(C7,C5,"y")&amp;"/"&amp;(DATEDIF(C7,C5,"m")-(DATEDIF(C7,C5,"y")*12)))</f>
-        <v>59/6</v>
+        <v>53/4</v>
       </c>
       <c r="D8" s="549" t="s">
-        <v>429</v>
+        <v>493</v>
       </c>
       <c r="E8" s="549"/>
       <c r="F8" s="549"/>
@@ -5936,8 +5936,8 @@
       <c r="G9" s="544"/>
       <c r="H9" s="545"/>
       <c r="I9" s="540" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"1.*"),"Early Retirement H&amp;W Pension Options",IF(COUNTIF(D8,"2.*"),"Regular at 62 H&amp;W Pension Options",IF(COUNTIF(D8,"3.*"),"Regular at 62 &amp; Early H&amp;W Pension Options",IF(COUNTIF(D8,"4.*"),"Regular at 62 &amp; Disability H&amp;W Pension Options",IF(COUNTIF(D8,"5.*"),"Regular at 65 H&amp;W Pension Options",IF(COUNTIF(D8,"6.*"),"Disability H&amp;W Pension Options",IF(COUNTIF(D8,"7.*"),"Service Pre-Age 55 H&amp;W Pension Options",IF(COUNTIF(D8,"8.*"),"Service Pre-Age 55 &amp; Disability H&amp;W Pension Options",IF(COUNTIF(D8,"9.*"),"Service H&amp;W Pension Options","Additional H&amp;W Options"))))))))))</f>
-        <v>Service H&amp;W Pension Options</v>
+        <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"1.*"),"Early Retirement H&amp;W Pension Options",IF(COUNTIF(D8,"2.*"),"Regular at 62 H&amp;W Pension Options",IF(COUNTIF(D8,"3.*"),"Regular at 62 &amp; Early H&amp;W Pension Options",IF(COUNTIF(D8,"4.*"),"Regular at 62 H&amp;W Pension Options",IF(COUNTIF(D8,"5.*"),"Regular at 65 H&amp;W Pension Options",IF(COUNTIF(D8,"6.*"),"Disability H&amp;W Pension Options",IF(COUNTIF(D8,"7.*"),"Service Pre-Age 55 H&amp;W Pension Options",IF(COUNTIF(D8,"8.*"),"Service Pre-Age 55 H&amp;W Pension Options",IF(COUNTIF(D8,"9.*"),"Service H&amp;W Pension Options","Additional H&amp;W Options"))))))))))</f>
+        <v>Service Pre-Age 55 H&amp;W Pension Options</v>
       </c>
       <c r="J9" s="541"/>
       <c r="K9" s="541"/>
@@ -5961,7 +5961,7 @@
       <c r="G10" s="546"/>
       <c r="H10" s="21">
         <f>SUM(A11:A17,A20:A21,A24:A29)</f>
-        <v>33.72</v>
+        <v>7.33</v>
       </c>
       <c r="I10" s="11" t="str">
         <f>IF(COUNTIF(C7,""),"","Option")</f>
@@ -5994,27 +5994,27 @@
       <c r="F11" s="539"/>
       <c r="G11" s="21">
         <f>SUM(A11:A17)</f>
-        <v>18.48</v>
+        <v>7.33</v>
       </c>
       <c r="H11" s="3">
         <f>C18</f>
-        <v>2202.7600000000002</v>
+        <v>876</v>
       </c>
       <c r="I11" s="16" t="str">
         <f>IF(COUNTIF(C7,""),"","50%")</f>
         <v>50%</v>
       </c>
-      <c r="J11" s="102">
+      <c r="J11" s="102" t="str">
         <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"4.*"),IF(COUNTIF(K6,"*Younger*"),100%-8%-(J6*0.4%),IF(100%-8%+(J6*0.4%)&gt;100%,100%,100%-8%+(J6*0.4%)))*100&amp;"% / "&amp;IF(COUNTIF(K6,"*Younger*"),100%-18%-(J6*0.4%),IF(100%-18%+(J6*0.4%)&gt;100%,100%,100%-18%+(J6*0.4%)))*100&amp;"%",IF(COUNTIF(D8,"6.*"),IF(COUNTIF(K6,"*Younger*"),100%-18%-(J6*0.4%),IF(100%-18%+(J6*0.4%)&gt;100%,100%,100%-18%+(J6*0.4%))),IF(COUNTIF(D8,"8.*"),IF(COUNTIF(K6,"*Younger*"),100%-8%-(J6*0.4%),IF(100%-8%+(J6*0.4%)&gt;100%,100%,100%-8%+(J6*0.4%)))*100&amp;"% / "&amp;IF(COUNTIF(K6,"*Younger*"),100%-18%-(J6*0.4%),IF(100%-18%+(J6*0.4%)&gt;100%,100%,100%-18%+(J6*0.4%)))*100&amp;"%",IF(COUNTIF(K6,"*Younger*"),100%-8%-(J6*0.4%),IF(100%-8%+(J6*0.4%)&gt;100%,100%,100%-8%+(J6*0.4%)))))))</f>
-        <v>0.92</v>
+        <v>88.8% / 78.8%</v>
       </c>
       <c r="K11" s="31">
         <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"1.*"),(H13+H16+H19)*J11,IF(COUNTIF(D8,"2.*"),(H11)*J11,IF(COUNTIF(D8,"3.*"),(H11+H16+H19)*J11,IF(COUNTIF(D8,"5.*"),(H11+H14+H17)*J11,IF(COUNTIF(D8,"6.*"),(H11+H14+H17)*J11,IF(COUNTIF(D8,"7.*"),(H11+H14)*J11,IF(COUNTIF(D8,"8.*"),(H11+H14)*IF(COUNTIF(K6,"*Younger*"),100%-8%-(J6*0.4%),IF(100%-8%+(J6*0.4%)&gt;100%,100%,100%-8%+(J6*0.4%)))+(H17*IF(COUNTIF(K6,"*Younger*"),100%-18%-(J6*0.4%),IF(100%-18%+(J6*0.4%)&gt;100%,100%,100%-18%+(J6*0.4%)))),IF(COUNTIF(D8,"4.*"),H11*IF(COUNTIF(K6,"*Younger*"),100%-8%-(J6*0.4%),IF(100%-8%+(J6*0.4%)&gt;100%,100%,100%-8%+(J6*0.4%)))+(H14+H17)*IF(COUNTIF(K6,"*Younger*"),100%-18%-(J6*0.4%),IF(100%-18%+(J6*0.4%)&gt;100%,100%,100%-18%+(J6*0.4%))),IF(COUNTIF(D8,"9.*"),(H11+H14+H17)*J11,""))))))))))</f>
-        <v>3883.2832000000003</v>
+        <v>777.88800000000003</v>
       </c>
       <c r="L11" s="5">
         <f>IF(COUNTIF(C7,""),"",K11*I11)</f>
-        <v>1941.6416000000002</v>
+        <v>388.94400000000002</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -6036,17 +6036,17 @@
         <f>IF(COUNTIF(C7,""),"","13th Check")</f>
         <v>13th Check</v>
       </c>
-      <c r="J12" s="102">
+      <c r="J12" s="102" t="str">
         <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"4.*"),IF(COUNTIF(K6,"*Younger*"),100%-8%-(J6*0.4%),IF(100%-8%+(J6*0.4%)&gt;100%,100%,100%-8%+(J6*0.4%)))*100&amp;"% / "&amp;IF(COUNTIF(K6,"*Younger*"),100%-18%-(J6*0.4%),IF(100%-18%+(J6*0.4%)&gt;100%,100%,100%-18%+(J6*0.4%)))*100&amp;"%",IF(COUNTIF(D8,"6.*"),IF(COUNTIF(K6,"*Younger*"),100%-18%-(J6*0.4%),IF(100%-18%+(J6*0.4%)&gt;100%,100%,100%-18%+(J6*0.4%))),IF(COUNTIF(D8,"8.*"),IF(COUNTIF(K6,"*Younger*"),100%-8%-(J6*0.4%),IF(100%-8%+(J6*0.4%)&gt;100%,100%,100%-8%+(J6*0.4%)))*100&amp;"% / "&amp;IF(COUNTIF(K6,"*Younger*"),100%-18%-(J6*0.4%),IF(100%-18%+(J6*0.4%)&gt;100%,100%,100%-18%+(J6*0.4%)))*100&amp;"%",IF(COUNTIF(K6,"*Younger*"),100%-8%-(J6*0.4%),IF(100%-8%+(J6*0.4%)&gt;100%,100%,100%-8%+(J6*0.4%)))))))</f>
-        <v>0.92</v>
+        <v>88.8% / 78.8%</v>
       </c>
       <c r="K12" s="31">
         <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"1.*"),(H13+H16+H19)*J12,IF(COUNTIF(D8,"2.*"),(H11)*J12,IF(COUNTIF(D8,"3.*"),(H11+H16+H19)*J12,IF(COUNTIF(D8,"5.*"),(H11+H14+H17)*J12,IF(COUNTIF(D8,"6.*"),(H11+H14+H17)*J12,IF(COUNTIF(D8,"7.*"),(H11+H14)*J12,IF(COUNTIF(D8,"8.*"),(H11+H14)*IF(COUNTIF(K6,"*Younger*"),100%-8%-(J6*0.4%),IF(100%-8%+(J6*0.4%)&gt;100%,100%,100%-8%+(J6*0.4%)))+(H17*IF(COUNTIF(K6,"*Younger*"),100%-18%-(J6*0.4%),IF(100%-18%+(J6*0.4%)&gt;100%,100%,100%-18%+(J6*0.4%)))),IF(COUNTIF(D8,"4.*"),H11*IF(COUNTIF(K6,"*Younger*"),100%-8%-(J6*0.4%),IF(100%-8%+(J6*0.4%)&gt;100%,100%,100%-8%+(J6*0.4%)))+(H14+H17)*IF(COUNTIF(K6,"*Younger*"),100%-18%-(J6*0.4%),IF(100%-18%+(J6*0.4%)&gt;100%,100%,100%-18%+(J6*0.4%))),IF(COUNTIF(D8,"9.*"),(H11+H14+H17)*J12,""))))))))))</f>
-        <v>3883.2832000000003</v>
+        <v>777.88800000000003</v>
       </c>
       <c r="L12" s="5">
         <f>IF(COUNTIF(C7,""),"",K12*I11)</f>
-        <v>1941.6416000000002</v>
+        <v>388.94400000000002</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -6071,17 +6071,17 @@
         <f>IF(COUNTIF(C7,""),"","75%")</f>
         <v>75%</v>
       </c>
-      <c r="J13" s="102">
+      <c r="J13" s="102" t="str">
         <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"4.*"),IF(COUNTIF(K6,"*Younger*"),100%-12%-(J6*0.4%),IF(100%-12%+(J6*0.4%)&gt;100%,100%,100%-12%+(J6*0.4%)))*100&amp;"% / "&amp;IF(COUNTIF(K6,"*Younger*"),100%-24%-(J6*0.4%),IF(100%-24%+(J6*0.4%)&gt;100%,100%,100%-24%+(J6*0.4%)))*100&amp;"%",IF(COUNTIF(D8,"6.*"),IF(COUNTIF(K6,"*Younger*"),100%-24%-(J6*0.4%),IF(100%-24%+(J6*0.4%)&gt;100%,100%,100%-24%+(J6*0.4%))),IF(COUNTIF(D8,"8.*"),IF(COUNTIF(K6,"*Younger*"),100%-12%-(J6*0.4%),IF(100%-12%+(J6*0.4%)&gt;100%,100%,100%-12%+(J6*0.4%)))*100&amp;"% / "&amp;IF(COUNTIF(K6,"*Younger*"),100%-24%-(J6*0.4%),IF(100%-24%+(J6*0.4%)&gt;100%,100%,100%-24%+(J6*0.4%)))*100&amp;"%",IF(COUNTIF(K6,"*Younger*"),100%-12%-(J6*0.4%),IF(100%-12%+(J6*0.4%)&gt;100%,100%,100%-12%+(J6*0.4%)))))))</f>
-        <v>0.88</v>
+        <v>84.8% / 72.8%</v>
       </c>
       <c r="K13" s="31">
         <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"1.*"),(H13+H16+H19)*J13,IF(COUNTIF(D8,"2.*"),(H11)*J13,IF(COUNTIF(D8,"3.*"),(H11+H16+H19)*J13,IF(COUNTIF(D8,"5.*"),(H11+H14+H17)*J13,IF(COUNTIF(D8,"6.*"),(H11+H14+H17)*J13,IF(COUNTIF(D8,"7.*"),(H11+H14)*J13,IF(COUNTIF(D8,"8.*"),(H11+H14)*IF(COUNTIF(K6,"*Younger*"),100%-12%-(J6*0.4%),IF(100%-12%+(J6*0.4%)&gt;100%,100%,100%-12%+(J6*0.4%)))+(H17*IF(COUNTIF(K6,"*Younger*"),100%-24%-(J6*0.4%),IF(100%-24%+(J6*0.4%)&gt;100%,100%,100%-24%+(J6*0.4%)))),IF(COUNTIF(D8,"4.*"),H11*IF(COUNTIF(K6,"*Younger*"),100%-12%-(J6*0.4%),IF(100%-12%+(J6*0.4%)&gt;100%,100%,100%-12%+(J6*0.4%)))+(H14+H17)*IF(COUNTIF(K6,"*Younger*"),100%-24%-(J6*0.4%),IF(100%-24%+(J6*0.4%)&gt;100%,100%,100%-24%+(J6*0.4%))),IF(COUNTIF(D8,"9.*"),(H11+H14+H17)*J13,""))))))))))</f>
-        <v>3714.4448000000002</v>
+        <v>742.84799999999996</v>
       </c>
       <c r="L13" s="5">
         <f>IF(COUNTIF(C7,""),"",K13*I13)</f>
-        <v>2785.8335999999999</v>
+        <v>557.13599999999997</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -6101,39 +6101,39 @@
       <c r="F14" s="539"/>
       <c r="G14" s="21">
         <f>SUM(A20:A21)</f>
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3">
         <f>C22</f>
-        <v>490</v>
+        <v>0</v>
       </c>
       <c r="I14" s="6" t="str">
         <f>IF(COUNTIF(C7,""),"","13th Check")</f>
         <v>13th Check</v>
       </c>
-      <c r="J14" s="102">
+      <c r="J14" s="102" t="str">
         <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"4.*"),IF(COUNTIF(K6,"*Younger*"),100%-12%-(J6*0.4%),IF(100%-12%+(J6*0.4%)&gt;100%,100%,100%-12%+(J6*0.4%)))*100&amp;"% / "&amp;IF(COUNTIF(K6,"*Younger*"),100%-24%-(J6*0.4%),IF(100%-24%+(J6*0.4%)&gt;100%,100%,100%-24%+(J6*0.4%)))*100&amp;"%",IF(COUNTIF(D8,"6.*"),IF(COUNTIF(K6,"*Younger*"),100%-24%-(J6*0.4%),IF(100%-24%+(J6*0.4%)&gt;100%,100%,100%-24%+(J6*0.4%))),IF(COUNTIF(D8,"8.*"),IF(COUNTIF(K6,"*Younger*"),100%-12%-(J6*0.4%),IF(100%-12%+(J6*0.4%)&gt;100%,100%,100%-12%+(J6*0.4%)))*100&amp;"% / "&amp;IF(COUNTIF(K6,"*Younger*"),100%-24%-(J6*0.4%),IF(100%-24%+(J6*0.4%)&gt;100%,100%,100%-24%+(J6*0.4%)))*100&amp;"%",IF(COUNTIF(K6,"*Younger*"),100%-12%-(J6*0.4%),IF(100%-12%+(J6*0.4%)&gt;100%,100%,100%-12%+(J6*0.4%)))))))</f>
-        <v>0.88</v>
+        <v>84.8% / 72.8%</v>
       </c>
       <c r="K14" s="31">
         <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"1.*"),(H13+H16+H19)*J14,IF(COUNTIF(D8,"2.*"),(H11)*J14,IF(COUNTIF(D8,"3.*"),(H11+H16+H19)*J14,IF(COUNTIF(D8,"5.*"),(H11+H14+H17)*J14,IF(COUNTIF(D8,"6.*"),(H11+H14+H17)*J14,IF(COUNTIF(D8,"7.*"),(H11+H14)*J14,IF(COUNTIF(D8,"8.*"),(H11+H14)*IF(COUNTIF(K6,"*Younger*"),100%-12%-(J6*0.4%),IF(100%-12%+(J6*0.4%)&gt;100%,100%,100%-12%+(J6*0.4%)))+(H17*IF(COUNTIF(K6,"*Younger*"),100%-24%-(J6*0.4%),IF(100%-24%+(J6*0.4%)&gt;100%,100%,100%-24%+(J6*0.4%)))),IF(COUNTIF(D8,"4.*"),H11*IF(COUNTIF(K6,"*Younger*"),100%-12%-(J6*0.4%),IF(100%-12%+(J6*0.4%)&gt;100%,100%,100%-12%+(J6*0.4%)))+(H14+H17)*IF(COUNTIF(K6,"*Younger*"),100%-24%-(J6*0.4%),IF(100%-24%+(J6*0.4%)&gt;100%,100%,100%-24%+(J6*0.4%))),IF(COUNTIF(D8,"9.*"),(H11+H14+H17)*J14,""))))))))))</f>
-        <v>3714.4448000000002</v>
+        <v>742.84799999999996</v>
       </c>
       <c r="L14" s="5">
         <f>IF(COUNTIF(C7,""),"",K14*I13)</f>
-        <v>2785.8335999999999</v>
+        <v>557.13599999999997</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="38">
-        <v>15.32</v>
+        <v>5.75</v>
       </c>
       <c r="B15" s="31">
         <v>118</v>
       </c>
       <c r="C15" s="5">
         <f t="shared" si="0"/>
-        <v>1807.76</v>
+        <v>678.5</v>
       </c>
       <c r="D15" s="2" t="str">
         <f>IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*")),"ER Factor","")</f>
@@ -6148,17 +6148,17 @@
         <f>IF(COUNTIF(C7,""),"","100%")</f>
         <v>100%</v>
       </c>
-      <c r="J15" s="102">
+      <c r="J15" s="102" t="str">
         <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"4.*"),IF(COUNTIF(K6,"*Younger*"),100%-15%-(J6*0.5%),IF(100%-15%+(J6*0.5%)&gt;100%,100%,100%-15%+(J6*0.5%)))*100&amp;"% / "&amp;IF(COUNTIF(K6,"*Younger*"),100%-30%-(J6*0.5%),IF(100%-30%+(J6*0.5%)&gt;100%,100%,100%-30%+(J6*0.5%)))*100&amp;"%",IF(COUNTIF(D8,"6.*"),IF(COUNTIF(K6,"*Younger*"),100%-30%-(J6*0.5%),IF(100%-30%+(J6*0.5%)&gt;100%,100%,100%-30%+(J6*0.5%))),IF(COUNTIF(D8,"8.*"),IF(COUNTIF(K6,"*Younger*"),100%-15%-(J6*0.5%),IF(100%-15%+(J6*0.5%)&gt;100%,100%,100%-15%+(J6*0.5%)))*100&amp;"% / "&amp;IF(COUNTIF(K6,"*Younger*"),100%-30%-(J6*0.5%),IF(100%-30%+(J6*0.5%)&gt;100%,100%,100%-30%+(J6*0.5%)))*100&amp;"%",IF(COUNTIF(K6,"*Younger*"),100%-15%-(J6*0.5%),IF(100%-15%+(J6*0.5%)&gt;100%,100%,100%-15%+(J6*0.5%)))))))</f>
-        <v>0.85</v>
+        <v>81% / 66%</v>
       </c>
       <c r="K15" s="31">
         <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"1.*"),(H13+H16+H19)*J15,IF(COUNTIF(D8,"2.*"),(H11)*J15,IF(COUNTIF(D8,"3.*"),(H11+H16+H19)*J15,IF(COUNTIF(D8,"5.*"),(H11+H14+H17)*J15,IF(COUNTIF(D8,"6.*"),(H11+H14+H17)*J15,IF(COUNTIF(D8,"7.*"),(H11+H14)*J15,IF(COUNTIF(D8,"8.*"),(H11+H14)*IF(COUNTIF(K6,"*Younger*"),100%-15%-(J6*0.5%),IF(100%-15%+(J6*0.5%)&gt;100%,100%,100%-15%+(J6*0.5%)))+(H17*IF(COUNTIF(K6,"*Younger*"),100%-30%-(J6*0.5%),IF(100%-30%+(J6*0.5%)&gt;100%,100%,100%-30%+(J6*0.5%)))),IF(COUNTIF(D8,"4.*"),H11*IF(COUNTIF(K6,"*Younger*"),100%-15%-(J6*0.5%),IF(100%-15%+(J6*0.5%)&gt;100%,100%,100%-15%+(J6*0.5%)))+(H14+H17)*IF(COUNTIF(K6,"*Younger*"),100%-30%-(J6*0.5%),IF(100%-30%+(J6*0.5%)&gt;100%,100%,100%-30%+(J6*0.5%))),IF(COUNTIF(D8,"9.*"),(H11+H14+H17)*J15,""))))))))))</f>
-        <v>3587.8159999999998</v>
+        <v>709.56</v>
       </c>
       <c r="L15" s="5">
         <f>IF(COUNTIF(C7,""),"",K15*I15)</f>
-        <v>3587.8159999999998</v>
+        <v>709.56</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -6185,29 +6185,29 @@
         <f>IF(COUNTIF(C7,""),"","13th Check")</f>
         <v>13th Check</v>
       </c>
-      <c r="J16" s="105">
+      <c r="J16" s="105" t="str">
         <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"4.*"),IF(COUNTIF(K6,"*Younger*"),100%-15%-(J6*0.5%),IF(100%-15%+(J6*0.5%)&gt;100%,100%,100%-15%+(J6*0.5%)))*100&amp;"% / "&amp;IF(COUNTIF(K6,"*Younger*"),100%-30%-(J6*0.5%),IF(100%-30%+(J6*0.5%)&gt;100%,100%,100%-30%+(J6*0.5%)))*100&amp;"%",IF(COUNTIF(D8,"6.*"),IF(COUNTIF(K6,"*Younger*"),100%-30%-(J6*0.5%),IF(100%-30%+(J6*0.5%)&gt;100%,100%,100%-30%+(J6*0.5%))),IF(COUNTIF(D8,"8.*"),IF(COUNTIF(K6,"*Younger*"),100%-15%-(J6*0.5%),IF(100%-15%+(J6*0.5%)&gt;100%,100%,100%-15%+(J6*0.5%)))*100&amp;"% / "&amp;IF(COUNTIF(K6,"*Younger*"),100%-30%-(J6*0.5%),IF(100%-30%+(J6*0.5%)&gt;100%,100%,100%-30%+(J6*0.5%)))*100&amp;"%",IF(COUNTIF(K6,"*Younger*"),100%-15%-(J6*0.5%),IF(100%-15%+(J6*0.5%)&gt;100%,100%,100%-15%+(J6*0.5%)))))))</f>
-        <v>0.85</v>
+        <v>81% / 66%</v>
       </c>
       <c r="K16" s="92">
         <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"1.*"),(H13+H16+H19)*J16,IF(COUNTIF(D8,"2.*"),(H11)*J16,IF(COUNTIF(D8,"3.*"),(H11+H16+H19)*J16,IF(COUNTIF(D8,"5.*"),(H11+H14+H17)*J16,IF(COUNTIF(D8,"6.*"),(H11+H14+H17)*J16,IF(COUNTIF(D8,"7.*"),(H11+H14)*J16,IF(COUNTIF(D8,"8.*"),(H11+H14)*IF(COUNTIF(K6,"*Younger*"),100%-15%-(J6*0.5%),IF(100%-15%+(J6*0.5%)&gt;100%,100%,100%-15%+(J6*0.5%)))+(H17*IF(COUNTIF(K6,"*Younger*"),100%-30%-(J6*0.5%),IF(100%-30%+(J6*0.5%)&gt;100%,100%,100%-30%+(J6*0.5%)))),IF(COUNTIF(D8,"4.*"),H11*IF(COUNTIF(K6,"*Younger*"),100%-15%-(J6*0.5%),IF(100%-15%+(J6*0.5%)&gt;100%,100%,100%-15%+(J6*0.5%)))+(H14+H17)*IF(COUNTIF(K6,"*Younger*"),100%-30%-(J6*0.5%),IF(100%-30%+(J6*0.5%)&gt;100%,100%,100%-30%+(J6*0.5%))),IF(COUNTIF(D8,"9.*"),(H11+H14+H17)*J16,""))))))))))</f>
-        <v>3587.8159999999998</v>
+        <v>709.56</v>
       </c>
       <c r="L16" s="85">
         <f>IF(COUNTIF(C7,""),"",K16*I15)</f>
-        <v>3587.8159999999998</v>
+        <v>709.56</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
-        <v>3.16</v>
+        <v>1.58</v>
       </c>
       <c r="B17" s="31">
         <v>125</v>
       </c>
       <c r="C17" s="5">
         <f t="shared" si="0"/>
-        <v>395</v>
+        <v>197.5</v>
       </c>
       <c r="D17" s="539" t="str">
         <f>"Member Benefit on and After 10/01/2014"</f>
@@ -6217,24 +6217,24 @@
       <c r="F17" s="539"/>
       <c r="G17" s="21">
         <f>SUM(A24:A29)</f>
-        <v>11.32</v>
+        <v>0</v>
       </c>
       <c r="H17" s="3">
         <f>C30</f>
-        <v>1528.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="24">
         <f>SUM(A11:A17)</f>
-        <v>18.48</v>
+        <v>7.33</v>
       </c>
       <c r="B18" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="26">
         <f>SUM(C11:C17)</f>
-        <v>2202.7600000000002</v>
+        <v>876</v>
       </c>
       <c r="D18" s="1" t="str">
         <f>IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),"ER Factor","")</f>
@@ -6245,8 +6245,8 @@
         <v/>
       </c>
       <c r="I18" s="540" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"1.*"),"Pension Benefit Deferred at Age 65 H&amp;W Options",IF(COUNTIF(D8,"2.*"),"Regular at 62 &amp; Early H&amp;W Options",IF(OR(COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),"Pension Benefit Service Pre-55 with Early H&amp;W Options",""))))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"1.*"),"Pension Benefit Deferred at Age 65 H&amp;W Options",IF(COUNTIF(D8,"2.*"),"Regular at 62 &amp; Early H&amp;W Options",IF(OR(COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),"Pension Benefit Regular at 62 with Early H&amp;W Options",IF(COUNTIF(D8,"4.*"),"Disability after 09/01/2011 H&amp;W Options",IF(COUNTIF(D8,"8.*"),"Disability after 10/01/2014 H&amp;W Options",""))))))</f>
+        <v>Disability after 10/01/2014 H&amp;W Options</v>
       </c>
       <c r="J18" s="541"/>
       <c r="K18" s="541"/>
@@ -6270,20 +6270,20 @@
         <v/>
       </c>
       <c r="I19" s="11" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),"Option",""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*"),COUNTIF(D8,"8.*")),"Option",""))</f>
+        <v>Option</v>
       </c>
       <c r="J19" s="80" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),"Factor",""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*"),COUNTIF(D8,"8.*")),"Factor",""))</f>
+        <v>Factor</v>
       </c>
       <c r="K19" s="80" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),"Member Benefit",""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*"),COUNTIF(D8,"8.*")),"Member Benefit",""))</f>
+        <v>Member Benefit</v>
       </c>
       <c r="L19" s="103" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),"Spouse Benefit",""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*"),COUNTIF(D8,"8.*")),"Spouse Benefit",""))</f>
+        <v>Spouse Benefit</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -6298,12 +6298,12 @@
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="I20" s="16" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),"50%",""))</f>
-        <v/>
-      </c>
-      <c r="J20" s="102" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),IF(COUNTIF(K6,"*Younger*"),100%-8%-(J6*0.4%),IF(100%-8%+(J6*0.4%)&gt;100%,100%,100%-8%+(J6*0.4%))),""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*"),COUNTIF(D8,"8.*")),"50%",""))</f>
+        <v>50%</v>
+      </c>
+      <c r="J20" s="102">
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),IF(COUNTIF(K6,"*Younger*"),100%-8%-(J6*0.4%),IF(100%-8%+(J6*0.4%)&gt;100%,100%,100%-8%+(J6*0.4%))),IF(OR(COUNTIF(D8,"4.*"),COUNTIF(D8,"8.*")),IF(COUNTIF(K6,"*Younger*"),100%-18%-(J6*0.4%),IF(100%-18%+(J6*0.4%)&gt;100%,100%,100%-18%+(J6*0.4%))),"")))</f>
+        <v>0.78800000000000003</v>
       </c>
       <c r="K20" s="31" t="str">
         <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"1.*"),(H27*J20),IF(COUNTIF(D8,"2.*"),(H11+H16+H19)*J20,IF(COUNTIF(D8,"3.*"),(H11+H14+H17)*J20,IF(COUNTIF(D8,"7.*"),(H11+H14+H19)*J20,"")))))</f>
@@ -6315,34 +6315,32 @@
       </c>
     </row>
     <row r="21" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="38">
-        <v>3.92</v>
-      </c>
+      <c r="A21" s="38"/>
       <c r="B21" s="31">
         <v>125</v>
       </c>
       <c r="C21" s="5">
         <f>A21*B21</f>
-        <v>490</v>
+        <v>0</v>
       </c>
       <c r="D21" s="101" t="str">
         <f>IF(COUNTIF(D8,"1.*"),"Member Early Retirement Pension Amount",IF(COUNTIF(D8,"2.*"),"Member Regular Retirement Pension at 62 Amount",IF(COUNTIF(D8,"3.*"),"Member Regular at 62 &amp; Early Retirement Pension Amount",IF(COUNTIF(D8,"4.*"),"Member Regular Retirement at 62 &amp; Disability Pension Amount",IF(COUNTIF(D8,"5.*"),"Member Regular Retirement Pension at 65 Amount",IF(COUNTIF(D8,"6.*"),"Member Disability Pension Amount",IF(COUNTIF(D8,"7.*"),"Member Pre-Age 55 Service",IF(COUNTIF(D8,"8.*"),"Member Pre-Age 55 Service &amp; Disability Pension Amount",IF(COUNTIF(D8,"9.*"),"Member  Service Pension Amount","")))))))))</f>
-        <v>Member  Service Pension Amount</v>
+        <v>Member Pre-Age 55 Service &amp; Disability Pension Amount</v>
       </c>
       <c r="E21" s="101"/>
       <c r="F21" s="101"/>
       <c r="G21" s="101"/>
       <c r="H21" s="100">
         <f>IF(COUNTIF(D8,"1.*"),SUM(H13,H16,H19),IF(COUNTIF(D8,"2.*"),H11,IF(COUNTIF(D8,"3.*"),SUM(H11,H16,H19),IF(COUNTIF(D8,"4.*"),SUM(H11,H14,H17),IF(COUNTIF(D8,"5.*"),SUM(H11,H14,H17),IF(COUNTIF(D8,"6.*"),SUM(H11,H14,H17),IF(COUNTIF(D8,"7.*"),SUM(H11,H14),IF(COUNTIF(D8,"8.*"),SUM(H11,H14,H17),IF(COUNTIF(D8,"9.*"),SUM(H11,H14,H17),"")))))))))</f>
-        <v>4220.96</v>
+        <v>876</v>
       </c>
       <c r="I21" s="6" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),"13th Check",""))</f>
-        <v/>
-      </c>
-      <c r="J21" s="102" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),IF(COUNTIF(K6,"*Younger*"),100%-8%-(J6*0.4%),IF(100%-8%+(J6*0.4%)&gt;100%,100%,100%-8%+(J6*0.4%))),""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*"),COUNTIF(D8,"8.*")),"13th Check",""))</f>
+        <v>13th Check</v>
+      </c>
+      <c r="J21" s="102">
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),IF(COUNTIF(K6,"*Younger*"),100%-8%-(J6*0.4%),IF(100%-8%+(J6*0.4%)&gt;100%,100%,100%-8%+(J6*0.4%))),IF(OR(COUNTIF(D8,"4.*"),COUNTIF(D8,"8.*")),IF(COUNTIF(K6,"*Younger*"),100%-18%-(J6*0.4%),IF(100%-18%+(J6*0.4%)&gt;100%,100%,100%-18%+(J6*0.4%))),"")))</f>
+        <v>0.78800000000000003</v>
       </c>
       <c r="K21" s="31" t="str">
         <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"1.*"),(H27*J21),IF(COUNTIF(D8,"2.*"),(H11+H16+H19)*J21,IF(COUNTIF(D8,"3.*"),(H11+H14+H17)*J21,IF(COUNTIF(D8,"7.*"),(H11+H14+H19)*J21,"")))))</f>
@@ -6356,14 +6354,14 @@
     <row r="22" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="24">
         <f>SUM(A20:A21)</f>
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="B22" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="26">
         <f>SUM(C20:C21)</f>
-        <v>490</v>
+        <v>0</v>
       </c>
       <c r="D22" s="101" t="s">
         <v>88</v>
@@ -6373,15 +6371,15 @@
       <c r="G22" s="101"/>
       <c r="H22" s="100">
         <f>IF(COUNTIF(D8,"1.*"),SUM(H13,H16,H19),IF(COUNTIF(D8,"2.*"),H11,IF(COUNTIF(D8,"3.*"),SUM(H11,H16,H19),IF(COUNTIF(D8,"4.*"),SUM(H11,H14,H17),IF(COUNTIF(D8,"5.*"),SUM(H11,H14,H17),IF(COUNTIF(D8,"6.*"),SUM(H11,H14,H17),IF(COUNTIF(D8,"7.*"),SUM(H11,H14),IF(COUNTIF(D8,"8.*"),SUM(H11,H14,H17),IF(COUNTIF(D8,"9.*"),SUM(H11,H14,H17),"")))))))))</f>
-        <v>4220.96</v>
+        <v>876</v>
       </c>
       <c r="I22" s="6" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),"75%",""))</f>
-        <v/>
-      </c>
-      <c r="J22" s="104" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),IF(COUNTIF(K6,"*Younger*"),100%-12%-(J6*0.4%),IF(100%-12%+(J6*0.4%)&gt;100%,100%,100%-12%+(J6*0.4%))),""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*"),COUNTIF(D8,"8.*")),"75%",""))</f>
+        <v>75%</v>
+      </c>
+      <c r="J22" s="104">
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),IF(COUNTIF(K6,"*Younger*"),100%-12%-(J6*0.4%),IF(100%-12%+(J6*0.4%)&gt;100%,100%,100%-12%+(J6*0.4%))),IF(OR(COUNTIF(D8,"4.*"),COUNTIF(D8,"8.*")),IF(COUNTIF(K6,"*Younger*"),100%-24%-(J6*0.4%),IF(100%-24%+(J6*0.4%)&gt;100%,100%,100%-24%+(J6*0.4%))),"")))</f>
+        <v>0.72799999999999998</v>
       </c>
       <c r="K22" s="31" t="str">
         <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"1.*"),(H27*J22),IF(COUNTIF(D8,"2.*"),(H11+H16+H19)*J22,IF(COUNTIF(D8,"3.*"),(H11+H14+H17)*J22,IF(COUNTIF(D8,"7.*"),(H11+H14+H19)*J22,"")))))</f>
@@ -6399,12 +6397,12 @@
       <c r="B23" s="537"/>
       <c r="C23" s="538"/>
       <c r="I23" s="16" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),"13th Check",""))</f>
-        <v/>
-      </c>
-      <c r="J23" s="102" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),IF(COUNTIF(K6,"*Younger*"),100%-12%-(J6*0.4%),IF(100%-12%+(J6*0.4%)&gt;100%,100%,100%-12%+(J6*0.4%))),""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*"),COUNTIF(D8,"8.*")),"13th Check",""))</f>
+        <v>13th Check</v>
+      </c>
+      <c r="J23" s="102">
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),IF(COUNTIF(K6,"*Younger*"),100%-12%-(J6*0.4%),IF(100%-12%+(J6*0.4%)&gt;100%,100%,100%-12%+(J6*0.4%))),IF(OR(COUNTIF(D8,"4.*"),COUNTIF(D8,"8.*")),IF(COUNTIF(K6,"*Younger*"),100%-24%-(J6*0.4%),IF(100%-24%+(J6*0.4%)&gt;100%,100%,100%-24%+(J6*0.4%))),"")))</f>
+        <v>0.72799999999999998</v>
       </c>
       <c r="K23" s="31" t="str">
         <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"1.*"),(H27*J23),IF(COUNTIF(D8,"2.*"),(H11+H16+H19)*J23,IF(COUNTIF(D8,"3.*"),(H11+H14+H17)*J23,IF(COUNTIF(D8,"7.*"),(H11+H14+H19)*J23,"")))))</f>
@@ -6436,12 +6434,12 @@
         <v/>
       </c>
       <c r="I24" s="6" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),"100%",""))</f>
-        <v/>
-      </c>
-      <c r="J24" s="102" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),IF(COUNTIF(K6,"*Younger*"),100%-15%-(J6*0.5%),IF(100%-15%+(J6*0.5%)&gt;100%,100%,100%-15%+(J6*0.5%))),""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*"),COUNTIF(D8,"8.*")),"100%",""))</f>
+        <v>100%</v>
+      </c>
+      <c r="J24" s="102">
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),IF(COUNTIF(K6,"*Younger*"),100%-15%-(J6*0.5%),IF(100%-15%+(J6*0.5%)&gt;100%,100%,100%-15%+(J6*0.5%))),IF(OR(COUNTIF(D8,"4.*"),COUNTIF(D8,"8.*")),IF(COUNTIF(K6,"*Younger*"),100%-30%-(J6*0.5%),IF(100%-30%+(J6*0.5%)&gt;100%,100%,100%-30%+(J6*0.5%))),"")))</f>
+        <v>0.65999999999999992</v>
       </c>
       <c r="K24" s="31" t="str">
         <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"1.*"),(H27*J24),IF(COUNTIF(D8,"2.*"),(H11+H16+H19)*J24,IF(COUNTIF(D8,"3.*"),(H11+H14+H17)*J24,IF(COUNTIF(D8,"7.*"),(H11+H14+H19)*J24,"")))))</f>
@@ -6473,12 +6471,12 @@
         <v/>
       </c>
       <c r="I25" s="106" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),"13th Check",""))</f>
-        <v/>
-      </c>
-      <c r="J25" s="105" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),IF(COUNTIF(K6,"*Younger*"),100%-15%-(J6*0.5%),IF(100%-15%+(J6*0.5%)&gt;100%,100%,100%-15%+(J6*0.5%))),""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*"),COUNTIF(D8,"8.*")),"13th Check",""))</f>
+        <v>13th Check</v>
+      </c>
+      <c r="J25" s="105">
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"1.*"),COUNTIF(D8,"2.*"),COUNTIF(D8,"3.*"),COUNTIF(D8,"7.*")),IF(COUNTIF(K6,"*Younger*"),100%-15%-(J6*0.5%),IF(100%-15%+(J6*0.5%)&gt;100%,100%,100%-15%+(J6*0.5%))),IF(OR(COUNTIF(D8,"4.*"),COUNTIF(D8,"8.*")),IF(COUNTIF(K6,"*Younger*"),100%-30%-(J6*0.5%),IF(100%-30%+(J6*0.5%)&gt;100%,100%,100%-30%+(J6*0.5%))),"")))</f>
+        <v>0.65999999999999992</v>
       </c>
       <c r="K25" s="92" t="str">
         <f>IF(COUNTIF(C7,""),"",IF(COUNTIF(D8,"1.*"),(H27*J25),IF(COUNTIF(D8,"2.*"),(H11+H16+H19)*J25,IF(COUNTIF(D8,"3.*"),(H11+H14+H17)*J25,IF(COUNTIF(D8,"7.*"),(H11+H14+H19)*J25,"")))))</f>
@@ -6490,15 +6488,13 @@
       </c>
     </row>
     <row r="26" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="38">
-        <v>11.32</v>
-      </c>
+      <c r="A26" s="38"/>
       <c r="B26" s="31">
         <v>135</v>
       </c>
       <c r="C26" s="5">
         <f t="shared" si="1"/>
-        <v>1528.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -6517,8 +6513,8 @@
         <v/>
       </c>
       <c r="I27" s="540" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*")),"Pension Benefit Deferred at Age 65 H&amp;W Options",""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*")),"Pension Benefit Deferred at Age 65 H&amp;W Options",IF(COUNTIF(D8,"4.*"),"Regular at 62 &amp; Disability H&amp;W Combined Pension Options",IF(COUNTIF(D8,"8.*"),"Service Pre-Age 55 &amp; Disability H&amp;W Combined Pension Options",""))))</f>
+        <v>Service Pre-Age 55 &amp; Disability H&amp;W Combined Pension Options</v>
       </c>
       <c r="J27" s="541"/>
       <c r="K27" s="541"/>
@@ -6540,20 +6536,20 @@
         <v/>
       </c>
       <c r="I28" s="79" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*")),"Option",""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*"),COUNTIF(D8,"8.*")),"Option",""))</f>
+        <v>Option</v>
       </c>
       <c r="J28" s="80" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*")),"Factor",""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*"),COUNTIF(D8,"8.*")),"Factor",""))</f>
+        <v>Factor</v>
       </c>
       <c r="K28" s="80" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*")),"Member Benefit",""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*"),COUNTIF(D8,"8.*")),"Member Benefit",""))</f>
+        <v>Member Benefit</v>
       </c>
       <c r="L28" s="81" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*")),"Spouse Benefit",""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*"),COUNTIF(D8,"8.*")),"Spouse Benefit",""))</f>
+        <v>Spouse Benefit</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -6564,8 +6560,8 @@
         <v>0</v>
       </c>
       <c r="I29" s="16" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*")),"50%",""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*"),COUNTIF(D8,"8.*")),"50%",""))</f>
+        <v>50%</v>
       </c>
       <c r="J29" s="102" t="str">
         <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*")),IF(COUNTIF(K6,"*Younger*"),100%-8%-(J6*0.4%),IF(100%-8%+(J6*0.4%)&gt;100%,100%,100%-8%+(J6*0.4%))),""))</f>
@@ -6583,20 +6579,20 @@
     <row r="30" spans="1:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="24">
         <f>SUM(A24:A29)</f>
-        <v>11.32</v>
+        <v>0</v>
       </c>
       <c r="B30" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="26">
         <f>SUM(C24:C29)</f>
-        <v>1528.2</v>
+        <v>0</v>
       </c>
       <c r="D30" s="77"/>
       <c r="H30" s="3"/>
       <c r="I30" s="6" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*")),"13th Check",""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*"),COUNTIF(D8,"8.*")),"13th Check",""))</f>
+        <v>13th Check</v>
       </c>
       <c r="J30" s="102" t="str">
         <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*")),IF(COUNTIF(K6,"*Younger*"),100%-8%-(J6*0.4%),IF(100%-8%+(J6*0.4%)&gt;100%,100%,100%-8%+(J6*0.4%))),""))</f>
@@ -6614,20 +6610,20 @@
     <row r="31" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="24">
         <f>SUM(A18,A22,A30)</f>
-        <v>33.72</v>
+        <v>7.33</v>
       </c>
       <c r="B31" s="28" t="s">
         <v>37</v>
       </c>
       <c r="C31" s="26">
         <f>SUM(C18,C22,C30)</f>
-        <v>4220.96</v>
+        <v>876</v>
       </c>
       <c r="D31" s="77"/>
       <c r="H31" s="3"/>
       <c r="I31" s="16" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*")),"75%",""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*"),COUNTIF(D8,"8.*")),"75%",""))</f>
+        <v>75%</v>
       </c>
       <c r="J31" s="102" t="str">
         <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*")),IF(COUNTIF(K6,"*Younger*"),100%-12%-(J6*0.4%),IF(100%-12%+(J6*0.4%)&gt;100%,100%,100%-12%+(J6*0.4%))),""))</f>
@@ -6644,8 +6640,8 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="I32" s="6" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*")),"13th Check",""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*"),COUNTIF(D8,"8.*")),"13th Check",""))</f>
+        <v>13th Check</v>
       </c>
       <c r="J32" s="102" t="str">
         <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*")),IF(COUNTIF(K6,"*Younger*"),100%-12%-(J6*0.4%),IF(100%-12%+(J6*0.4%)&gt;100%,100%,100%-12%+(J6*0.4%))),""))</f>
@@ -6662,8 +6658,8 @@
     </row>
     <row r="33" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I33" s="16" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*")),"100%",""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*"),COUNTIF(D8,"8.*")),"100%",""))</f>
+        <v>100%</v>
       </c>
       <c r="J33" s="102" t="str">
         <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*")),IF(COUNTIF(K6,"*Younger*"),100%-15%-(J6*0.5%),IF(100%-15%+(J6*0.5%)&gt;100%,100%,100%-15%+(J6*0.5%))),""))</f>
@@ -6696,8 +6692,8 @@
       <c r="G34" s="78"/>
       <c r="H34" s="93"/>
       <c r="I34" s="18" t="str">
-        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*")),"13th Check",""))</f>
-        <v/>
+        <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*"),COUNTIF(D8,"8.*")),"13th Check",""))</f>
+        <v>13th Check</v>
       </c>
       <c r="J34" s="105" t="str">
         <f>IF(COUNTIF(C7,""),"",IF(OR(COUNTIF(D8,"2.*"),COUNTIF(D8,"7.*")),IF(COUNTIF(K6,"*Younger*"),100%-15%-(J6*0.5%),IF(100%-15%+(J6*0.5%)&gt;100%,100%,100%-15%+(J6*0.5%))),""))</f>
@@ -6718,7 +6714,7 @@
       </c>
       <c r="B36" s="108">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C36" s="78"/>
       <c r="D36" s="78"/>
@@ -6727,7 +6723,7 @@
       </c>
       <c r="F36" s="108">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="G36" s="78"/>
       <c r="H36" s="78"/>
@@ -6949,7 +6945,7 @@
   <sheetData>
     <row r="4" spans="1:8" x14ac:dyDescent="1.4">
       <c r="A4" s="588" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B4" s="588"/>
       <c r="C4" s="588"/>
@@ -6975,21 +6971,21 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="1.4">
       <c r="A6" s="525" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B6" s="589"/>
       <c r="C6" s="589"/>
       <c r="D6" s="589"/>
       <c r="E6" s="589"/>
       <c r="F6" s="525" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="G6" s="589"/>
       <c r="H6" s="589"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="1.4">
       <c r="A7" s="525" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B7" s="526"/>
       <c r="C7" s="526"/>
@@ -7013,7 +7009,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="1.4">
       <c r="A9" s="525" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B9" s="526"/>
       <c r="C9" s="526"/>
@@ -7025,7 +7021,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="1.4">
       <c r="A10" s="525" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="B10" s="589"/>
       <c r="C10" s="589"/>
@@ -7037,7 +7033,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="1.4">
       <c r="A11" s="525" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B11" s="526"/>
       <c r="C11" s="526"/>
@@ -7053,7 +7049,7 @@
       </c>
       <c r="B12" s="527">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C12" s="526"/>
       <c r="D12" s="526"/>
@@ -7064,7 +7060,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="1.4">
       <c r="A13" s="588" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="B13" s="588"/>
       <c r="C13" s="588"/>
@@ -7076,7 +7072,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="1.4">
       <c r="A14" s="588" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B14" s="588"/>
       <c r="C14" s="588"/>
@@ -7088,7 +7084,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="1.4">
       <c r="A15" s="525" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="B15" s="525"/>
       <c r="C15" s="525"/>
@@ -7100,7 +7096,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="1.4">
       <c r="A16" s="525" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B16" s="528">
         <v>46174</v>
@@ -8287,14 +8283,14 @@
         <v>323</v>
       </c>
       <c r="B3" s="402" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C3" s="101"/>
       <c r="D3" s="101" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="402" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F3" s="401" t="s">
         <v>324</v>
@@ -9344,7 +9340,7 @@
       </c>
       <c r="G38" s="483">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="39" spans="2:12" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -13632,13 +13628,13 @@
         <v>392</v>
       </c>
       <c r="B2" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -13701,7 +13697,7 @@
         <v>2094.949999999998</v>
       </c>
       <c r="F5" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="I5" s="480"/>
       <c r="J5" s="196"/>
@@ -15216,7 +15212,7 @@
       <c r="L4" s="78"/>
       <c r="M4" s="555">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="N4" s="555"/>
     </row>
@@ -16958,7 +16954,7 @@
       </c>
       <c r="M4" s="108">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="N4" s="178"/>
       <c r="O4" s="178"/>
@@ -19286,7 +19282,7 @@
       </c>
       <c r="M4" s="108">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="N4" s="178"/>
       <c r="O4" s="178"/>
@@ -21353,7 +21349,7 @@
       <c r="C2" s="546"/>
       <c r="D2" s="667" t="str">
         <f>'Pension Calculator'!C2</f>
-        <v>Charles W. Welch</v>
+        <v>Rigoberto Pimentel</v>
       </c>
       <c r="E2" s="667"/>
       <c r="F2" s="667"/>
@@ -21362,7 +21358,7 @@
       </c>
       <c r="J2" s="666" t="str">
         <f>'Pension Calculator'!I2</f>
-        <v>329932X80</v>
+        <v>320395X00</v>
       </c>
       <c r="K2" s="666"/>
     </row>
@@ -21374,7 +21370,7 @@
       <c r="C3" s="546"/>
       <c r="D3" s="14">
         <f>'Pension Calculator'!C3</f>
-        <v>24372</v>
+        <v>23105</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21385,7 +21381,7 @@
       <c r="C4" s="546"/>
       <c r="D4" s="20" t="str">
         <f>DATEDIF(D3,D5,"y")&amp;"/"&amp;(DATEDIF(D3,D5, "m") - (DATEDIF(D3,D5, "y") * 12))</f>
-        <v>59/8</v>
+        <v>62/3</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21396,7 +21392,7 @@
       <c r="C5" s="546"/>
       <c r="D5" s="14">
         <f>'Pension Calculator'!C5</f>
-        <v>46174</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21407,7 +21403,7 @@
       <c r="C6" s="546"/>
       <c r="D6" s="666" t="str">
         <f>'Pension Calculator'!C6</f>
-        <v>Xiomara Welch</v>
+        <v>Perla S. Pimentel</v>
       </c>
       <c r="E6" s="666"/>
       <c r="F6" s="666"/>
@@ -21418,11 +21414,11 @@
       <c r="J6" s="546"/>
       <c r="K6" s="12">
         <f>IF(D7=0,0,IF(AND(D3-D7&lt;0,(DATEDIF(D3,D5,"m")-(DATEDIF(D3,D5,"y")*12))-(DATEDIF(D7,D5,"m")-(DATEDIF(D7,D5,"y")*12))=0),DATEDIF(D3,D5,"y")-DATEDIF(D7,D5,"y"),IF(AND(D3-D7&gt;0,(DATEDIF(D7,D5,"m")-(DATEDIF(D7,D5,"y")*12))-(DATEDIF(D3,D5,"m")-(DATEDIF(D3,D5,"y")*12))=0),DATEDIF(D7,D5,"y")-DATEDIF(D3,D5,"y"),IF(D3-D7&lt;0,ROUNDDOWN(YEARFRAC(D3,D7),0),IF(D3-D7&gt;0,ROUNDDOWN(YEARFRAC(D7,D3),0),0)))))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L6" s="1" t="str">
         <f>IF(D7=0,"N/A",IF(K6=0,"No Difference.",IF(D3-D7&lt;0,"Year(s) Younger.", IF(D3-D7&gt;0, "Year(s) Older.","No Difference."))))</f>
-        <v>No Difference.</v>
+        <v>Year(s) Younger.</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21433,7 +21429,7 @@
       <c r="C7" s="546"/>
       <c r="D7" s="14">
         <f>'Pension Calculator'!C7</f>
-        <v>24432</v>
+        <v>26366</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -21444,7 +21440,7 @@
       <c r="C8" s="575"/>
       <c r="D8" s="20" t="str">
         <f>DATEDIF(D7,D5,"y")&amp;"/"&amp;(DATEDIF(D7,D5, "m") - (DATEDIF(D7,D5, "y") * 12))</f>
-        <v>59/6</v>
+        <v>53/4</v>
       </c>
       <c r="E8" s="19"/>
       <c r="F8" s="19"/>
@@ -21526,15 +21522,15 @@
       </c>
       <c r="K11" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-8%-(K6*0.4%),IF(100%-8%+(K6*0.4%)&gt;100%,100%,100%-8%+(K6*0.4%)))</f>
-        <v>0.92</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="L11" s="3">
         <f>(I15+I18+I21)*K11</f>
-        <v>1388.3559653568002</v>
+        <v>1608.6078082404001</v>
       </c>
       <c r="M11" s="7">
         <f>L11*J11</f>
-        <v>694.1779826784001</v>
+        <v>804.30390412020006</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -21557,15 +21553,15 @@
       </c>
       <c r="K12" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-8%-(K6*0.4%),IF(100%-8%+(K6*0.4%)&gt;100%,100%,100%-8%+(K6*0.4%)))</f>
-        <v>0.92</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="L12" s="3">
         <f>(I15+I18)*K12</f>
-        <v>642.59208742080023</v>
+        <v>724.70595368160002</v>
       </c>
       <c r="M12" s="7">
         <f>L12*J11</f>
-        <v>321.29604371040011</v>
+        <v>362.35297684080001</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -21594,15 +21590,15 @@
       </c>
       <c r="K13" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-12%-(K6*0.4%),IF(100%-12%+(K6*0.4%)&gt;100%,100%,100%-12%+(K6*0.4%)))</f>
-        <v>0.88</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="L13" s="3">
         <f>(I15+I18+I21)*K13</f>
-        <v>1327.9926625152002</v>
+        <v>1536.1479970584001</v>
       </c>
       <c r="M13" s="7">
         <f>L13*J13</f>
-        <v>995.99449688640016</v>
+        <v>1152.1109977937999</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -21620,22 +21616,22 @@
       </c>
       <c r="I14" s="4">
         <f>IF(DATEDIF(D3,D5,"m")&lt;=600,(DATEDIF(D3,D5,"m")-540)*0.1%+40%,IF(DATEDIF(D3,D5,"m")&lt;=660,(DATEDIF(D3,D5,"m")-600)*0.2%+46%,IF((DATEDIF(D3,D5,"m")-660)*0.5%+58%&gt;=100%,100%,(DATEDIF(D3,D5,"m")-660)*0.5%+58%)))</f>
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>25</v>
       </c>
       <c r="K14" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-12%-(K6*0.4%),IF(100%-12%+(K6*0.4%)&gt;100%,100%,100%-12%+(K6*0.4%)))</f>
-        <v>0.88</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="L14" s="3">
         <f>(I15+I18)*K14</f>
-        <v>614.65330101120014</v>
+        <v>692.06154135360009</v>
       </c>
       <c r="M14" s="7">
         <f>L14*J13</f>
-        <v>460.98997575840008</v>
+        <v>519.04615601520004</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -21659,22 +21655,22 @@
       </c>
       <c r="I15" s="3">
         <f>(I13*I14)</f>
-        <v>638.05130664000012</v>
+        <v>741.9201240000001</v>
       </c>
       <c r="J15" s="16">
         <v>1</v>
       </c>
       <c r="K15" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-15%-(K6*0.5%),IF(100%-15%+(K6*0.5%)&gt;100%,100%,100%-15%+(K6*0.4%)))</f>
-        <v>0.85</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="L15" s="3">
         <f>(I15+I18+I21)*K15</f>
-        <v>1282.7201853840002</v>
+        <v>1467.3111764354999</v>
       </c>
       <c r="M15" s="7">
         <f>L15*J15</f>
-        <v>1282.7201853840002</v>
+        <v>1467.3111764354999</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -21706,15 +21702,15 @@
       </c>
       <c r="K16" s="22">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-15%-(K6*0.5%),IF(100%-15%+(K6*0.5%)&gt;100%,100%,100%-15%+(K6*0.4%)))</f>
-        <v>0.85</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="L16" s="8">
         <f>(I15+I18)*K16</f>
-        <v>593.69921120400011</v>
+        <v>661.04934964200004</v>
       </c>
       <c r="M16" s="9">
         <f>L16*J15</f>
-        <v>593.69921120400011</v>
+        <v>661.04934964200004</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -21733,7 +21729,7 @@
       <c r="F17" s="2"/>
       <c r="I17" s="4">
         <f>IF(DATEDIF(D3,D5,"m")&lt;=600,(DATEDIF(D3,D5,"m")-540)*0.1%+22%,IF(DATEDIF(D3,D5,"m")&lt;=660,(DATEDIF(D3,D5,"m")-600)*0.2%+28%,IF((DATEDIF(D3,D5,"m")-660)*0.5%+40%&gt;=100%,100%,(DATEDIF(D3,D5,"m")-660)*0.5%+40%)))</f>
-        <v>0.68</v>
+        <v>0.83499999999999996</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -21757,7 +21753,7 @@
       </c>
       <c r="I18" s="3">
         <f>I16*I17</f>
-        <v>60.418353600000003</v>
+        <v>74.190184200000004</v>
       </c>
       <c r="J18" s="540" t="s">
         <v>28</v>
@@ -21815,22 +21811,22 @@
       </c>
       <c r="I20" s="4">
         <f>IF(DATEDIF(D3,D5,"m")&lt;=600,(DATEDIF(D3,D5,"m")-540)*0.1%+22%,IF(DATEDIF(D3,D5,"m")&lt;=660,(DATEDIF(D3,D5,"m")-600)*0.2%+28%,IF((DATEDIF(D3,D5,"m")-660)*0.5%+40%&gt;=100%,100%,(DATEDIF(D3,D5,"m")-660)*0.5%+40%)))</f>
-        <v>0.68</v>
+        <v>0.83499999999999996</v>
       </c>
       <c r="J20" s="16">
         <v>0.5</v>
       </c>
       <c r="K20" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-18%-(K6*0.4%),IF(100%-18%+(K6*0.4%)&gt;100%,100%,100%-18%+(K6*0.4%)))</f>
-        <v>0.82000000000000006</v>
+        <v>0.78800000000000003</v>
       </c>
       <c r="L20" s="3">
         <f>(I13+I16+I19)*K20</f>
-        <v>1658.7357322800001</v>
+        <v>1594.0045817519999</v>
       </c>
       <c r="M20" s="7">
         <f>L20*J20</f>
-        <v>829.36786614000005</v>
+        <v>797.00229087599996</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -21848,22 +21844,22 @@
       </c>
       <c r="I21" s="3">
         <f>I19*I20</f>
-        <v>810.61291080000001</v>
+        <v>995.38497135</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>25</v>
       </c>
       <c r="K21" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-18%-(K6*0.4%),IF(100%-18%+(K6*0.4%)&gt;100%,100%,100%-18%+(K6*0.4%)))</f>
-        <v>0.82000000000000006</v>
+        <v>0.78800000000000003</v>
       </c>
       <c r="L21" s="3">
         <f>(I13+I16)*K21</f>
-        <v>681.2319280800001</v>
+        <v>654.64726747200007</v>
       </c>
       <c r="M21" s="7">
         <f>L21*J20</f>
-        <v>340.61596404000005</v>
+        <v>327.32363373600003</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -21889,15 +21885,15 @@
       </c>
       <c r="K22" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-24%-(K6*0.4%),IF(100%-24%+(K6*0.4%)&gt;100%,100%,100%-24%+(K6*0.4%)))</f>
-        <v>0.76</v>
+        <v>0.72799999999999998</v>
       </c>
       <c r="L22" s="3">
         <f>(I13+I16+I19)*K22</f>
-        <v>1537.3648250399999</v>
+        <v>1472.633674512</v>
       </c>
       <c r="M22" s="7">
         <f>L22*J22</f>
-        <v>1153.0236187799999</v>
+        <v>1104.475255884</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -21919,15 +21915,15 @@
       </c>
       <c r="K23" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-24%-(K6*0.4%),IF(100%-24%+(K6*0.4%)&gt;100%,100%,100%-24%+(K6*0.4%)))</f>
-        <v>0.76</v>
+        <v>0.72799999999999998</v>
       </c>
       <c r="L23" s="3">
         <f>(I13+I16)*K23</f>
-        <v>631.38568944000008</v>
+        <v>604.80102883200004</v>
       </c>
       <c r="M23" s="7">
         <f>L23*J22</f>
-        <v>473.53926708000006</v>
+        <v>453.600771624</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -21957,15 +21953,15 @@
       </c>
       <c r="K24" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-30%-(K6*0.5%),IF(100%-30%+(K6*0.5%)&gt;100%,100%,100%-30%+(K6*0.4%)))</f>
-        <v>0.7</v>
+        <v>0.65999999999999992</v>
       </c>
       <c r="L24" s="3">
         <f>(I13+I16+I19)*K24</f>
-        <v>1415.9939178</v>
+        <v>1335.0799796399997</v>
       </c>
       <c r="M24" s="7">
         <f>L24*J24</f>
-        <v>1415.9939178</v>
+        <v>1335.0799796399997</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -21984,15 +21980,15 @@
       </c>
       <c r="K25" s="22">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-30%-(K6*0.5%),IF(100%-30%+(K6*0.5%)&gt;100%,100%,100%-30%+(K6*0.4%)))</f>
-        <v>0.7</v>
+        <v>0.65999999999999992</v>
       </c>
       <c r="L25" s="8">
         <f>(I13+I16)*K24</f>
-        <v>581.53945080000005</v>
+        <v>548.30862503999992</v>
       </c>
       <c r="M25" s="9">
         <f>L25*J24</f>
-        <v>581.53945080000005</v>
+        <v>548.30862503999992</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -22010,7 +22006,7 @@
       </c>
       <c r="I26" s="3">
         <f>SUM(I15,I18,I21)</f>
-        <v>1509.0825710400002</v>
+        <v>1811.4952795500001</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -22026,7 +22022,7 @@
       </c>
       <c r="I27" s="3">
         <f>SUM(I15,I18)</f>
-        <v>698.46966024000017</v>
+        <v>816.11030820000008</v>
       </c>
       <c r="J27" s="540" t="s">
         <v>69</v>
@@ -22069,15 +22065,15 @@
       </c>
       <c r="K29" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-8%-(K6*0.4%),IF(100%-8%+(K6*0.4%)&gt;100%,100%,100%-8%+(K6*0.4%)))</f>
-        <v>0.92</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="L29" s="3">
         <f>(I13+I16+I19)*K29</f>
-        <v>1861.0205776800001</v>
+        <v>1796.2894271519999</v>
       </c>
       <c r="M29" s="7">
         <f>L29*J29</f>
-        <v>930.51028884000004</v>
+        <v>898.14471357599996</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -22101,15 +22097,15 @@
       </c>
       <c r="K30" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-8%-(K6*0.4%),IF(100%-8%+(K6*0.4%)&gt;100%,100%,100%-8%+(K6*0.4%)))</f>
-        <v>0.92</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="L30" s="3">
         <f>(I13+I16)*K30</f>
-        <v>764.30899248000014</v>
+        <v>737.72433187200011</v>
       </c>
       <c r="M30" s="7">
         <f>L30*J29</f>
-        <v>382.15449624000007</v>
+        <v>368.86216593600005</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -22139,15 +22135,15 @@
       </c>
       <c r="K31" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-12%-(K6*0.4%),IF(100%-12%+(K6*0.4%)&gt;100%,100%,100%-12%+(K6*0.4%)))</f>
-        <v>0.88</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="L31" s="3">
         <f>(I13+I16+I19)*K31</f>
-        <v>1780.10663952</v>
+        <v>1715.3754889919999</v>
       </c>
       <c r="M31" s="7">
         <f>L31*J31</f>
-        <v>1335.0799796400001</v>
+        <v>1286.5316167439998</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -22168,15 +22164,15 @@
       </c>
       <c r="K32" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-12%-(K6*0.4%),IF(100%-12%+(K6*0.4%)&gt;100%,100%,100%-12%+(K6*0.4%)))</f>
-        <v>0.88</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="L32" s="3">
         <f>(I13+I16)*K32</f>
-        <v>731.07816672000001</v>
+        <v>704.49350611199998</v>
       </c>
       <c r="M32" s="7">
         <f>L32*J31</f>
-        <v>548.30862504000004</v>
+        <v>528.37012958399998</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22203,15 +22199,15 @@
       </c>
       <c r="K33" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-15%-(K6*0.5%),IF(100%-15%+(K6*0.5%)&gt;100%,100%,100%-15%+(K6*0.4%)))</f>
-        <v>0.85</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="L33" s="3">
         <f>(I13+I16+I19)*K33</f>
-        <v>1719.4211859</v>
+        <v>1638.5072477399999</v>
       </c>
       <c r="M33" s="7">
         <f>L33*J33</f>
-        <v>1719.4211859</v>
+        <v>1638.5072477399999</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -22236,15 +22232,15 @@
       </c>
       <c r="K34" s="22">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-15%-(K6*0.5%),IF(100%-15%+(K6*0.5%)&gt;100%,100%,100%-15%+(K6*0.4%)))</f>
-        <v>0.85</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="L34" s="8">
         <f>(I13+I16)*K34</f>
-        <v>706.15504740000006</v>
+        <v>672.92422164000004</v>
       </c>
       <c r="M34" s="9">
         <f>L34*J33</f>
-        <v>706.15504740000006</v>
+        <v>672.92422164000004</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -22328,15 +22324,15 @@
       </c>
       <c r="K38" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-8%-(K6*0.4%),IF(100%-8%+(K6*0.4%)&gt;100%,100%,100%-8%+(K6*0.4%)))</f>
-        <v>0.92</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="L38" s="3">
         <f>I36*K38</f>
-        <v>1088.3775526800002</v>
+        <v>1050.5209421520001</v>
       </c>
       <c r="M38" s="7">
         <f>L38*J38</f>
-        <v>544.18877634000012</v>
+        <v>525.26047107600004</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -22367,15 +22363,15 @@
       </c>
       <c r="K39" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-8%-(K6*0.4%),IF(100%-8%+(K6*0.4%)&gt;100%,100%,100%-8%+(K6*0.4%)))</f>
-        <v>0.92</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="L39" s="3">
         <f>I37*K39</f>
-        <v>764.30899248000014</v>
+        <v>737.72433187200022</v>
       </c>
       <c r="M39" s="7">
         <f>L39*J38</f>
-        <v>382.15449624000007</v>
+        <v>368.86216593600011</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -22406,15 +22402,15 @@
       </c>
       <c r="K40" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-12%-(K6*0.4%),IF(100%-12%+(K6*0.4%)&gt;100%,100%,100%-12%+(K6*0.4%)))</f>
-        <v>0.88</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="L40" s="3">
         <f>I36*K40</f>
-        <v>1041.0567895200002</v>
+        <v>1003.2001789920001</v>
       </c>
       <c r="M40" s="7">
         <f>L40*J40</f>
-        <v>780.79259214000012</v>
+        <v>752.40013424400013</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -22434,15 +22430,15 @@
       </c>
       <c r="K41" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-12%-(K6*0.4%),IF(100%-12%+(K6*0.4%)&gt;100%,100%,100%-12%+(K6*0.4%)))</f>
-        <v>0.88</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="L41" s="3">
         <f>I37*K41</f>
-        <v>731.07816672000013</v>
+        <v>704.49350611200009</v>
       </c>
       <c r="M41" s="7">
         <f>L41*J40</f>
-        <v>548.30862504000015</v>
+        <v>528.3701295840001</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
@@ -22451,15 +22447,15 @@
       </c>
       <c r="K42" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-15%-(K6*0.5%),IF(100%-15%+(K6*0.5%)&gt;100%,100%,100%-15%+(K6*0.4%)))</f>
-        <v>0.85</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="L42" s="3">
         <f>I36*K42</f>
-        <v>1005.5662171500001</v>
+        <v>958.2454539900001</v>
       </c>
       <c r="M42" s="7">
         <f>L42*J42</f>
-        <v>1005.5662171500001</v>
+        <v>958.2454539900001</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -22480,15 +22476,15 @@
       </c>
       <c r="K43" s="22">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-15%-(K6*0.5%),IF(100%-15%+(K6*0.5%)&gt;100%,100%,100%-15%+(K6*0.4%)))</f>
-        <v>0.85</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="L43" s="8">
         <f>I37*K43</f>
-        <v>706.15504740000017</v>
+        <v>672.92422164000004</v>
       </c>
       <c r="M43" s="9">
         <f>L43*J42</f>
-        <v>706.15504740000017</v>
+        <v>672.92422164000004</v>
       </c>
     </row>
   </sheetData>
@@ -23610,7 +23606,7 @@
       </c>
       <c r="E39" s="114">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F39" s="19"/>
       <c r="G39" s="19"/>
@@ -23729,7 +23725,7 @@
       <c r="C2" s="546"/>
       <c r="D2" s="667" t="str">
         <f>'Pension Calculator'!C2</f>
-        <v>Charles W. Welch</v>
+        <v>Rigoberto Pimentel</v>
       </c>
       <c r="E2" s="667"/>
       <c r="F2" s="667"/>
@@ -23738,7 +23734,7 @@
       </c>
       <c r="J2" s="666" t="str">
         <f>'Pension Calculator'!I2</f>
-        <v>329932X80</v>
+        <v>320395X00</v>
       </c>
       <c r="K2" s="666"/>
     </row>
@@ -23750,7 +23746,7 @@
       <c r="C3" s="546"/>
       <c r="D3" s="14">
         <f>'Pension Calculator'!C3</f>
-        <v>24372</v>
+        <v>23105</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23761,7 +23757,7 @@
       <c r="C4" s="546"/>
       <c r="D4" s="20" t="str">
         <f>DATEDIF(D3,D5,"y")&amp;"/"&amp;(DATEDIF(D3,D5, "m") - (DATEDIF(D3,D5, "y") * 12))</f>
-        <v>59/8</v>
+        <v>62/3</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23772,7 +23768,7 @@
       <c r="C5" s="546"/>
       <c r="D5" s="14">
         <f>'Pension Calculator'!C5</f>
-        <v>46174</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23783,7 +23779,7 @@
       <c r="C6" s="546"/>
       <c r="D6" s="666" t="str">
         <f>'Pension Calculator'!C6</f>
-        <v>Xiomara Welch</v>
+        <v>Perla S. Pimentel</v>
       </c>
       <c r="E6" s="666"/>
       <c r="F6" s="666"/>
@@ -23794,11 +23790,11 @@
       <c r="J6" s="546"/>
       <c r="K6" s="12">
         <f>IF(D7=0,0,IF(AND(D3-D7&lt;0,(DATEDIF(D3,D5,"m")-(DATEDIF(D3,D5,"y")*12))-(DATEDIF(D7,D5,"m")-(DATEDIF(D7,D5,"y")*12))=0),DATEDIF(D3,D5,"y")-DATEDIF(D7,D5,"y"),IF(AND(D3-D7&gt;0,(DATEDIF(D7,D5,"m")-(DATEDIF(D7,D5,"y")*12))-(DATEDIF(D3,D5,"m")-(DATEDIF(D3,D5,"y")*12))=0),DATEDIF(D7,D5,"y")-DATEDIF(D3,D5,"y"),IF(D3-D7&lt;0,ROUNDDOWN(YEARFRAC(D3,D7),0),IF(D3-D7&gt;0,ROUNDDOWN(YEARFRAC(D7,D3),0),0)))))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L6" s="1" t="str">
         <f>IF(D7=0,"N/A",IF(K6=0,"No Difference.",IF(D3-D7&lt;0,"Year(s) Younger.", IF(D3-D7&gt;0, "Year(s) Older.","No Difference."))))</f>
-        <v>No Difference.</v>
+        <v>Year(s) Younger.</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23809,7 +23805,7 @@
       <c r="C7" s="546"/>
       <c r="D7" s="14">
         <f>'Pension Calculator'!C7</f>
-        <v>24432</v>
+        <v>26366</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -23820,7 +23816,7 @@
       <c r="C8" s="575"/>
       <c r="D8" s="20" t="str">
         <f>DATEDIF(D7,D5,"y")&amp;"/"&amp;(DATEDIF(D7,D5, "m") - (DATEDIF(D7,D5, "y") * 12))</f>
-        <v>59/6</v>
+        <v>53/4</v>
       </c>
       <c r="E8" s="19"/>
       <c r="F8" s="19"/>
@@ -23902,15 +23898,15 @@
       </c>
       <c r="K11" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-8%-(K6*0.4%),IF(100%-8%+(K6*0.4%)&gt;100%,100%,100%-8%+(K6*0.4%)))</f>
-        <v>0.92</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="L11" s="3">
         <f>(I15+I18+I21)*K11</f>
-        <v>1388.3559653568002</v>
+        <v>1608.6078082404001</v>
       </c>
       <c r="M11" s="7">
         <f>L11*J11</f>
-        <v>694.1779826784001</v>
+        <v>804.30390412020006</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -23933,15 +23929,15 @@
       </c>
       <c r="K12" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-8%-(K6*0.4%),IF(100%-8%+(K6*0.4%)&gt;100%,100%,100%-8%+(K6*0.4%)))</f>
-        <v>0.92</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="L12" s="3">
         <f>(I15+I18)*K12</f>
-        <v>642.59208742080023</v>
+        <v>724.70595368160002</v>
       </c>
       <c r="M12" s="7">
         <f>L12*J11</f>
-        <v>321.29604371040011</v>
+        <v>362.35297684080001</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -23970,15 +23966,15 @@
       </c>
       <c r="K13" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-12%-(K6*0.4%),IF(100%-12%+(K6*0.4%)&gt;100%,100%,100%-12%+(K6*0.4%)))</f>
-        <v>0.88</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="L13" s="3">
         <f>(I15+I18+I21)*K13</f>
-        <v>1327.9926625152002</v>
+        <v>1536.1479970584001</v>
       </c>
       <c r="M13" s="7">
         <f>L13*J13</f>
-        <v>995.99449688640016</v>
+        <v>1152.1109977937999</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -23996,22 +23992,22 @@
       </c>
       <c r="I14" s="4">
         <f>IF(DATEDIF(D3,D5,"m")&lt;=600,(DATEDIF(D3,D5,"m")-540)*0.1%+40%,IF(DATEDIF(D3,D5,"m")&lt;=660,(DATEDIF(D3,D5,"m")-600)*0.2%+46%,IF((DATEDIF(D3,D5,"m")-660)*0.5%+58%&gt;=100%,100%,(DATEDIF(D3,D5,"m")-660)*0.5%+58%)))</f>
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>25</v>
       </c>
       <c r="K14" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-12%-(K6*0.4%),IF(100%-12%+(K6*0.4%)&gt;100%,100%,100%-12%+(K6*0.4%)))</f>
-        <v>0.88</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="L14" s="3">
         <f>(I15+I18)*K14</f>
-        <v>614.65330101120014</v>
+        <v>692.06154135360009</v>
       </c>
       <c r="M14" s="7">
         <f>L14*J13</f>
-        <v>460.98997575840008</v>
+        <v>519.04615601520004</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -24035,22 +24031,22 @@
       </c>
       <c r="I15" s="3">
         <f>(I13*I14)</f>
-        <v>638.05130664000012</v>
+        <v>741.9201240000001</v>
       </c>
       <c r="J15" s="16">
         <v>1</v>
       </c>
       <c r="K15" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-15%-(K6*0.5%),IF(100%-15%+(K6*0.5%)&gt;100%,100%,100%-15%+(K6*0.4%)))</f>
-        <v>0.85</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="L15" s="3">
         <f>(I15+I18+I21)*K15</f>
-        <v>1282.7201853840002</v>
+        <v>1467.3111764354999</v>
       </c>
       <c r="M15" s="7">
         <f>L15*J15</f>
-        <v>1282.7201853840002</v>
+        <v>1467.3111764354999</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -24082,15 +24078,15 @@
       </c>
       <c r="K16" s="22">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-15%-(K6*0.5%),IF(100%-15%+(K6*0.5%)&gt;100%,100%,100%-15%+(K6*0.4%)))</f>
-        <v>0.85</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="L16" s="8">
         <f>(I15+I18)*K16</f>
-        <v>593.69921120400011</v>
+        <v>661.04934964200004</v>
       </c>
       <c r="M16" s="9">
         <f>L16*J15</f>
-        <v>593.69921120400011</v>
+        <v>661.04934964200004</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -24109,7 +24105,7 @@
       <c r="F17" s="2"/>
       <c r="I17" s="4">
         <f>IF(DATEDIF(D3,D5,"m")&lt;=600,(DATEDIF(D3,D5,"m")-540)*0.1%+22%,IF(DATEDIF(D3,D5,"m")&lt;=660,(DATEDIF(D3,D5,"m")-600)*0.2%+28%,IF((DATEDIF(D3,D5,"m")-660)*0.5%+40%&gt;=100%,100%,(DATEDIF(D3,D5,"m")-660)*0.5%+40%)))</f>
-        <v>0.68</v>
+        <v>0.83499999999999996</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -24133,7 +24129,7 @@
       </c>
       <c r="I18" s="3">
         <f>I16*I17</f>
-        <v>60.418353600000003</v>
+        <v>74.190184200000004</v>
       </c>
       <c r="J18" s="540" t="s">
         <v>28</v>
@@ -24191,22 +24187,22 @@
       </c>
       <c r="I20" s="4">
         <f>IF(DATEDIF(D3,D5,"m")&lt;=600,(DATEDIF(D3,D5,"m")-540)*0.1%+22%,IF(DATEDIF(D3,D5,"m")&lt;=660,(DATEDIF(D3,D5,"m")-600)*0.2%+28%,IF((DATEDIF(D3,D5,"m")-660)*0.5%+40%&gt;=100%,100%,(DATEDIF(D3,D5,"m")-660)*0.5%+40%)))</f>
-        <v>0.68</v>
+        <v>0.83499999999999996</v>
       </c>
       <c r="J20" s="16">
         <v>0.5</v>
       </c>
       <c r="K20" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-18%-(K6*0.4%),IF(100%-18%+(K6*0.4%)&gt;100%,100%,100%-18%+(K6*0.4%)))</f>
-        <v>0.82000000000000006</v>
+        <v>0.78800000000000003</v>
       </c>
       <c r="L20" s="3">
         <f>(I13+I16+I19)*K20</f>
-        <v>1658.7357322800001</v>
+        <v>1594.0045817519999</v>
       </c>
       <c r="M20" s="7">
         <f>L20*J20</f>
-        <v>829.36786614000005</v>
+        <v>797.00229087599996</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -24224,22 +24220,22 @@
       </c>
       <c r="I21" s="3">
         <f>I19*I20</f>
-        <v>810.61291080000001</v>
+        <v>995.38497135</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>25</v>
       </c>
       <c r="K21" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-18%-(K6*0.4%),IF(100%-18%+(K6*0.4%)&gt;100%,100%,100%-18%+(K6*0.4%)))</f>
-        <v>0.82000000000000006</v>
+        <v>0.78800000000000003</v>
       </c>
       <c r="L21" s="3">
         <f>(I13+I16)*K21</f>
-        <v>681.2319280800001</v>
+        <v>654.64726747200007</v>
       </c>
       <c r="M21" s="7">
         <f>L21*J20</f>
-        <v>340.61596404000005</v>
+        <v>327.32363373600003</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -24265,15 +24261,15 @@
       </c>
       <c r="K22" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-24%-(K6*0.4%),IF(100%-24%+(K6*0.4%)&gt;100%,100%,100%-24%+(K6*0.4%)))</f>
-        <v>0.76</v>
+        <v>0.72799999999999998</v>
       </c>
       <c r="L22" s="3">
         <f>(I13+I16+I19)*K22</f>
-        <v>1537.3648250399999</v>
+        <v>1472.633674512</v>
       </c>
       <c r="M22" s="7">
         <f>L22*J22</f>
-        <v>1153.0236187799999</v>
+        <v>1104.475255884</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -24295,15 +24291,15 @@
       </c>
       <c r="K23" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-24%-(K6*0.4%),IF(100%-24%+(K6*0.4%)&gt;100%,100%,100%-24%+(K6*0.4%)))</f>
-        <v>0.76</v>
+        <v>0.72799999999999998</v>
       </c>
       <c r="L23" s="3">
         <f>(I13+I16)*K23</f>
-        <v>631.38568944000008</v>
+        <v>604.80102883200004</v>
       </c>
       <c r="M23" s="7">
         <f>L23*J22</f>
-        <v>473.53926708000006</v>
+        <v>453.600771624</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -24333,15 +24329,15 @@
       </c>
       <c r="K24" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-30%-(K6*0.5%),IF(100%-30%+(K6*0.5%)&gt;100%,100%,100%-30%+(K6*0.4%)))</f>
-        <v>0.7</v>
+        <v>0.65999999999999992</v>
       </c>
       <c r="L24" s="3">
         <f>(I13+I16+I19)*K24</f>
-        <v>1415.9939178</v>
+        <v>1335.0799796399997</v>
       </c>
       <c r="M24" s="7">
         <f>L24*J24</f>
-        <v>1415.9939178</v>
+        <v>1335.0799796399997</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -24360,15 +24356,15 @@
       </c>
       <c r="K25" s="22">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-30%-(K6*0.5%),IF(100%-30%+(K6*0.5%)&gt;100%,100%,100%-30%+(K6*0.4%)))</f>
-        <v>0.7</v>
+        <v>0.65999999999999992</v>
       </c>
       <c r="L25" s="8">
         <f>(I13+I16)*K24</f>
-        <v>581.53945080000005</v>
+        <v>548.30862503999992</v>
       </c>
       <c r="M25" s="9">
         <f>L25*J24</f>
-        <v>581.53945080000005</v>
+        <v>548.30862503999992</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -24386,7 +24382,7 @@
       </c>
       <c r="I26" s="3">
         <f>SUM(I15,I18,I21)</f>
-        <v>1509.0825710400002</v>
+        <v>1811.4952795500001</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -24402,7 +24398,7 @@
       </c>
       <c r="I27" s="3">
         <f>SUM(I15,I18)</f>
-        <v>698.46966024000017</v>
+        <v>816.11030820000008</v>
       </c>
       <c r="J27" s="540" t="s">
         <v>69</v>
@@ -24445,15 +24441,15 @@
       </c>
       <c r="K29" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-8%-(K6*0.4%),IF(100%-8%+(K6*0.4%)&gt;100%,100%,100%-8%+(K6*0.4%)))</f>
-        <v>0.92</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="L29" s="3">
         <f>(I13+I16+I19)*K29</f>
-        <v>1861.0205776800001</v>
+        <v>1796.2894271519999</v>
       </c>
       <c r="M29" s="7">
         <f>L29*J29</f>
-        <v>930.51028884000004</v>
+        <v>898.14471357599996</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -24477,15 +24473,15 @@
       </c>
       <c r="K30" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-8%-(K6*0.4%),IF(100%-8%+(K6*0.4%)&gt;100%,100%,100%-8%+(K6*0.4%)))</f>
-        <v>0.92</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="L30" s="3">
         <f>(I13+I16)*K30</f>
-        <v>764.30899248000014</v>
+        <v>737.72433187200011</v>
       </c>
       <c r="M30" s="7">
         <f>L30*J29</f>
-        <v>382.15449624000007</v>
+        <v>368.86216593600005</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -24515,15 +24511,15 @@
       </c>
       <c r="K31" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-12%-(K6*0.4%),IF(100%-12%+(K6*0.4%)&gt;100%,100%,100%-12%+(K6*0.4%)))</f>
-        <v>0.88</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="L31" s="3">
         <f>(I13+I16+I19)*K31</f>
-        <v>1780.10663952</v>
+        <v>1715.3754889919999</v>
       </c>
       <c r="M31" s="7">
         <f>L31*J31</f>
-        <v>1335.0799796400001</v>
+        <v>1286.5316167439998</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -24544,15 +24540,15 @@
       </c>
       <c r="K32" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-12%-(K6*0.4%),IF(100%-12%+(K6*0.4%)&gt;100%,100%,100%-12%+(K6*0.4%)))</f>
-        <v>0.88</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="L32" s="3">
         <f>(I13+I16)*K32</f>
-        <v>731.07816672000001</v>
+        <v>704.49350611199998</v>
       </c>
       <c r="M32" s="7">
         <f>L32*J31</f>
-        <v>548.30862504000004</v>
+        <v>528.37012958399998</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24579,15 +24575,15 @@
       </c>
       <c r="K33" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-15%-(K6*0.5%),IF(100%-15%+(K6*0.5%)&gt;100%,100%,100%-15%+(K6*0.4%)))</f>
-        <v>0.85</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="L33" s="3">
         <f>(I13+I16+I19)*K33</f>
-        <v>1719.4211859</v>
+        <v>1638.5072477399999</v>
       </c>
       <c r="M33" s="7">
         <f>L33*J33</f>
-        <v>1719.4211859</v>
+        <v>1638.5072477399999</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -24612,15 +24608,15 @@
       </c>
       <c r="K34" s="22">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-15%-(K6*0.5%),IF(100%-15%+(K6*0.5%)&gt;100%,100%,100%-15%+(K6*0.4%)))</f>
-        <v>0.85</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="L34" s="8">
         <f>(I13+I16)*K34</f>
-        <v>706.15504740000006</v>
+        <v>672.92422164000004</v>
       </c>
       <c r="M34" s="9">
         <f>L34*J33</f>
-        <v>706.15504740000006</v>
+        <v>672.92422164000004</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -24704,15 +24700,15 @@
       </c>
       <c r="K38" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-8%-(K6*0.4%),IF(100%-8%+(K6*0.4%)&gt;100%,100%,100%-8%+(K6*0.4%)))</f>
-        <v>0.92</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="L38" s="3">
         <f>I36*K38</f>
-        <v>1088.3775526800002</v>
+        <v>1050.5209421520001</v>
       </c>
       <c r="M38" s="7">
         <f>L38*J38</f>
-        <v>544.18877634000012</v>
+        <v>525.26047107600004</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -24743,15 +24739,15 @@
       </c>
       <c r="K39" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-8%-(K6*0.4%),IF(100%-8%+(K6*0.4%)&gt;100%,100%,100%-8%+(K6*0.4%)))</f>
-        <v>0.92</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="L39" s="3">
         <f>I37*K39</f>
-        <v>764.30899248000014</v>
+        <v>737.72433187200022</v>
       </c>
       <c r="M39" s="7">
         <f>L39*J38</f>
-        <v>382.15449624000007</v>
+        <v>368.86216593600011</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -24782,15 +24778,15 @@
       </c>
       <c r="K40" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-12%-(K6*0.4%),IF(100%-12%+(K6*0.4%)&gt;100%,100%,100%-12%+(K6*0.4%)))</f>
-        <v>0.88</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="L40" s="3">
         <f>I36*K40</f>
-        <v>1041.0567895200002</v>
+        <v>1003.2001789920001</v>
       </c>
       <c r="M40" s="7">
         <f>L40*J40</f>
-        <v>780.79259214000012</v>
+        <v>752.40013424400013</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -24810,15 +24806,15 @@
       </c>
       <c r="K41" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-12%-(K6*0.4%),IF(100%-12%+(K6*0.4%)&gt;100%,100%,100%-12%+(K6*0.4%)))</f>
-        <v>0.88</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="L41" s="3">
         <f>I37*K41</f>
-        <v>731.07816672000013</v>
+        <v>704.49350611200009</v>
       </c>
       <c r="M41" s="7">
         <f>L41*J40</f>
-        <v>548.30862504000015</v>
+        <v>528.3701295840001</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
@@ -24827,15 +24823,15 @@
       </c>
       <c r="K42" s="17">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-15%-(K6*0.5%),IF(100%-15%+(K6*0.5%)&gt;100%,100%,100%-15%+(K6*0.4%)))</f>
-        <v>0.85</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="L42" s="3">
         <f>I36*K42</f>
-        <v>1005.5662171500001</v>
+        <v>958.2454539900001</v>
       </c>
       <c r="M42" s="7">
         <f>L42*J42</f>
-        <v>1005.5662171500001</v>
+        <v>958.2454539900001</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
@@ -24856,15 +24852,15 @@
       </c>
       <c r="K43" s="22">
         <f>IF(COUNTIF(L6,"*Younger*"),100%-15%-(K6*0.5%),IF(100%-15%+(K6*0.5%)&gt;100%,100%,100%-15%+(K6*0.4%)))</f>
-        <v>0.85</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="L43" s="8">
         <f>I37*K43</f>
-        <v>706.15504740000017</v>
+        <v>672.92422164000004</v>
       </c>
       <c r="M43" s="9">
         <f>L43*J42</f>
-        <v>706.15504740000017</v>
+        <v>672.92422164000004</v>
       </c>
     </row>
   </sheetData>
@@ -27020,13 +27016,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="226" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F2" s="543" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="G2" s="543"/>
       <c r="K2" s="78" t="s">
@@ -27065,7 +27061,7 @@
       <c r="L4" s="78"/>
       <c r="M4" s="555">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="N4" s="555"/>
     </row>
@@ -28310,7 +28306,7 @@
     </row>
     <row r="34" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="567" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B34" s="568"/>
       <c r="C34" s="568"/>
@@ -28362,7 +28358,7 @@
         <v>AP 1 Name:</v>
       </c>
       <c r="B36" s="242" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C36" s="111" t="str">
         <f>IF(COUNTIF(A34,"Select*"),"","AP 1 DOB:")</f>
@@ -31684,7 +31680,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="576" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B1" s="576"/>
       <c r="C1" s="576"/>
@@ -31704,16 +31700,16 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="576" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B3" s="576"/>
       <c r="C3" s="529">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="D3" s="530">
         <f ca="1">NOW()</f>
-        <v>46163.687062847224</v>
+        <v>46164.659340509257</v>
       </c>
       <c r="E3" s="195"/>
       <c r="F3" s="195"/>
@@ -31724,7 +31720,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="195" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C4" s="529"/>
       <c r="D4" s="530"/>
@@ -31737,7 +31733,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="195" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C5" s="529"/>
       <c r="D5" s="530"/>
@@ -31747,7 +31743,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="195" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B6" s="529">
         <v>45809</v>
@@ -31760,7 +31756,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="195" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B7" s="529">
         <v>45809</v>
@@ -31773,7 +31769,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="195" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B8" s="529">
         <v>46143</v>
@@ -31786,7 +31782,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="195" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B9" s="529">
         <v>46147</v>
@@ -31799,19 +31795,19 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="195" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B10" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C10" t="s">
         <v>269</v>
       </c>
       <c r="D10" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="E10" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="G10" s="195"/>
     </row>
@@ -32160,7 +32156,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B26" s="196">
         <f>SUM(B11:B23)</f>
@@ -32172,7 +32168,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B27" s="196" t="e">
         <f>SUM(E11:E23)</f>
@@ -32184,7 +32180,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B28" s="196" t="e">
         <f>B27-B26</f>
@@ -32407,7 +32403,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="585" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B1" s="585"/>
       <c r="C1" s="585"/>
@@ -32420,7 +32416,7 @@
     </row>
     <row r="2" spans="1:11" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="585" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B2" s="585"/>
       <c r="C2" s="585"/>
@@ -32446,20 +32442,20 @@
     </row>
     <row r="5" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A5" s="484" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B5" s="484"/>
       <c r="C5" s="485" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D5" s="485"/>
       <c r="E5" s="485"/>
       <c r="F5" s="485"/>
       <c r="G5" s="486" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="H5" s="485" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="I5" s="485"/>
       <c r="J5" s="484"/>
@@ -32480,7 +32476,7 @@
     </row>
     <row r="7" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="484" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B7" s="484"/>
       <c r="C7" s="484"/>
@@ -32489,7 +32485,7 @@
       <c r="F7" s="484"/>
       <c r="G7" s="484"/>
       <c r="H7" s="487" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="I7" s="485"/>
       <c r="J7" s="484"/>
@@ -32575,7 +32571,7 @@
     </row>
     <row r="14" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="484" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B14" s="484"/>
       <c r="C14" s="487">
@@ -32584,7 +32580,7 @@
       <c r="D14" s="485"/>
       <c r="E14" s="484"/>
       <c r="F14" s="484" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="G14" s="484"/>
       <c r="H14" s="484"/>
@@ -32599,7 +32595,7 @@
       <c r="D15" s="484"/>
       <c r="E15" s="484"/>
       <c r="F15" s="490" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="G15" s="490"/>
       <c r="H15" s="490"/>
@@ -32609,7 +32605,7 @@
     </row>
     <row r="16" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A16" s="484" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B16" s="484"/>
       <c r="C16" s="487">
@@ -32618,7 +32614,7 @@
       <c r="D16" s="485"/>
       <c r="E16" s="484"/>
       <c r="F16" s="490" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="G16" s="490"/>
       <c r="H16" s="490"/>
@@ -32633,7 +32629,7 @@
       <c r="D17" s="484"/>
       <c r="E17" s="484"/>
       <c r="F17" s="490" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="G17" s="490"/>
       <c r="H17" s="490"/>
@@ -32648,7 +32644,7 @@
       <c r="D18" s="484"/>
       <c r="E18" s="484"/>
       <c r="F18" s="490" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="G18" s="490"/>
       <c r="H18" s="490"/>
@@ -32671,7 +32667,7 @@
     </row>
     <row r="20" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A20" s="491" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B20" s="491"/>
       <c r="C20" s="491"/>
@@ -32688,7 +32684,7 @@
     </row>
     <row r="21" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A21" s="491" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B21" s="491"/>
       <c r="C21" s="491"/>
@@ -32718,7 +32714,7 @@
     </row>
     <row r="23" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A23" s="491" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B23" s="491"/>
       <c r="C23" s="491"/>
@@ -32736,7 +32732,7 @@
     </row>
     <row r="24" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A24" s="491" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B24" s="491"/>
       <c r="C24" s="494">
@@ -32764,7 +32760,7 @@
     </row>
     <row r="26" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A26" s="496" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B26" s="511">
         <f>IF(C16&gt;36053,"",IF(AND(MONTH(C16)&lt;"6",YEAR(C16)=1998),YEAR(C16),IF(MONTH(C16)&lt;"5",YEAR(C16)+1,"")))</f>
@@ -32772,7 +32768,7 @@
       </c>
       <c r="C26" s="497"/>
       <c r="D26" s="498" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E26" s="499">
         <f>IF(B26=1981,0.055,IF(B26=1982,0.0845,IF(B26=1983,0.1017,IF(B26=1984,0.093807,IF(B26=1985,0.12604006,IF(B26=1986,0.08076508,IF(B26=1987,0.06066944,IF(B26=1988,0.06668109,IF(B26=1989,0.08438409,IF(B26=1990,0.08780206,IF(B26=1991,0.10655716,IF(B26=1992,0.1269022,IF(B26=1993,0.13044565,IF(B26=1994,0.0952,IF(B26=1995,0.07845,IF(B26=1996,0.04089,IF(B26=1997,0.06913,IF(B26=1998,0.0873744,""))))))))))))))))))</f>
@@ -32796,7 +32792,7 @@
       </c>
       <c r="F27" s="491"/>
       <c r="G27" s="484" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="H27" s="484"/>
       <c r="I27" s="484"/>
@@ -32807,7 +32803,7 @@
       <c r="A28" s="503"/>
       <c r="B28" s="504"/>
       <c r="C28" s="505" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D28" s="504"/>
       <c r="E28" s="506">
@@ -32836,7 +32832,7 @@
     </row>
     <row r="30" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A30" s="496" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B30" s="511">
         <f>IF(B26&gt;1997,"",B26+1)</f>
@@ -32844,7 +32840,7 @@
       </c>
       <c r="C30" s="497"/>
       <c r="D30" s="498" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E30" s="499">
         <f>IF(B30=1981,0.055,IF(B30=1982,0.0845,IF(B30=1983,0.1017,IF(B30=1984,0.093807,IF(B30=1985,0.12604006,IF(B30=1986,0.08076508,IF(B30=1987,0.06066944,IF(B30=1988,0.06668109,IF(B30=1989,0.08438409,IF(B30=1990,0.08780206,IF(B30=1991,0.10655716,IF(B30=1992,0.1269022,IF(B30=1993,0.13044565,IF(B30=1994,0.0952,IF(B30=1995,0.07845,IF(B30=1996,0.04089,IF(B30=1997,0.06913,IF(B30=1998,0.0873744,""))))))))))))))))))</f>
@@ -32868,11 +32864,11 @@
       </c>
       <c r="F31" s="491"/>
       <c r="G31" s="484" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="H31" s="487">
         <f ca="1">TODAY()</f>
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="I31" s="485"/>
       <c r="J31" s="484"/>
@@ -32882,7 +32878,7 @@
       <c r="A32" s="503"/>
       <c r="B32" s="504"/>
       <c r="C32" s="505" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D32" s="504"/>
       <c r="E32" s="508">
@@ -32904,7 +32900,7 @@
       <c r="E33" s="510"/>
       <c r="F33" s="484"/>
       <c r="G33" s="484" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="H33" s="484"/>
       <c r="I33" s="484"/>
@@ -32913,7 +32909,7 @@
     </row>
     <row r="34" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A34" s="496" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B34" s="511">
         <f>IF(B30&gt;1997,"",B30+1)</f>
@@ -32921,7 +32917,7 @@
       </c>
       <c r="C34" s="497"/>
       <c r="D34" s="498" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E34" s="499">
         <f>IF(B34=1981,0.055,IF(B34=1982,0.0845,IF(B34=1983,0.1017,IF(B34=1984,0.093807,IF(B34=1985,0.12604006,IF(B34=1986,0.08076508,IF(B34=1987,0.06066944,IF(B34=1988,0.06668109,IF(B34=1989,0.08438409,IF(B34=1990,0.08780206,IF(B34=1991,0.10655716,IF(B34=1992,0.1269022,IF(B34=1993,0.13044565,IF(B34=1994,0.0952,IF(B34=1995,0.07845,IF(B34=1996,0.04089,IF(B34=1997,0.06913,IF(B34=1998,0.0873744,""))))))))))))))))))</f>
@@ -32954,7 +32950,7 @@
       <c r="A36" s="503"/>
       <c r="B36" s="504"/>
       <c r="C36" s="505" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D36" s="504"/>
       <c r="E36" s="508">
@@ -32976,7 +32972,7 @@
       <c r="E37" s="267"/>
       <c r="F37" s="484"/>
       <c r="G37" s="484" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="H37" s="485"/>
       <c r="I37" s="485"/>
@@ -32985,7 +32981,7 @@
     </row>
     <row r="38" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A38" s="496" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B38" s="511">
         <f>IF(B34&gt;1997,"",B34+1)</f>
@@ -32993,7 +32989,7 @@
       </c>
       <c r="C38" s="497"/>
       <c r="D38" s="498" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E38" s="499">
         <f>IF(B38=1981,0.055,IF(B38=1982,0.0845,IF(B38=1983,0.1017,IF(B38=1984,0.093807,IF(B38=1985,0.12604006,IF(B38=1986,0.08076508,IF(B38=1987,0.06066944,IF(B38=1988,0.06668109,IF(B38=1989,0.08438409,IF(B38=1990,0.08780206,IF(B38=1991,0.10655716,IF(B38=1992,0.1269022,IF(B38=1993,0.13044565,IF(B38=1994,0.0952,IF(B38=1995,0.07845,IF(B38=1996,0.04089,IF(B38=1997,0.06913,IF(B38=1998,0.0873744,""))))))))))))))))))</f>
@@ -33026,7 +33022,7 @@
       <c r="A40" s="503"/>
       <c r="B40" s="504"/>
       <c r="C40" s="505" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D40" s="504"/>
       <c r="E40" s="508">
@@ -33055,7 +33051,7 @@
     </row>
     <row r="42" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A42" s="496" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B42" s="511">
         <f>IF(B38&gt;1997,"",B38+1)</f>
@@ -33063,7 +33059,7 @@
       </c>
       <c r="C42" s="497"/>
       <c r="D42" s="498" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E42" s="499">
         <f>IF(B42=1981,0.055,IF(B42=1982,0.0845,IF(B42=1983,0.1017,IF(B42=1984,0.093807,IF(B42=1985,0.12604006,IF(B42=1986,0.08076508,IF(B42=1987,0.06066944,IF(B42=1988,0.06668109,IF(B42=1989,0.08438409,IF(B42=1990,0.08780206,IF(B42=1991,0.10655716,IF(B42=1992,0.1269022,IF(B42=1993,0.13044565,IF(B42=1994,0.0952,IF(B42=1995,0.07845,IF(B42=1996,0.04089,IF(B42=1997,0.06913,IF(B42=1998,0.0873744,""))))))))))))))))))</f>
@@ -33096,7 +33092,7 @@
       <c r="A44" s="503"/>
       <c r="B44" s="504"/>
       <c r="C44" s="505" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D44" s="504"/>
       <c r="E44" s="508">
@@ -33125,7 +33121,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="496" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B46" s="511">
         <f>IF(B42&gt;1997,"",B42+1)</f>
@@ -33133,7 +33129,7 @@
       </c>
       <c r="C46" s="497"/>
       <c r="D46" s="498" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E46" s="499">
         <f>IF(B46=1981,0.055,IF(B46=1982,0.0845,IF(B46=1983,0.1017,IF(B46=1984,0.093807,IF(B46=1985,0.12604006,IF(B46=1986,0.08076508,IF(B46=1987,0.06066944,IF(B46=1988,0.06668109,IF(B46=1989,0.08438409,IF(B46=1990,0.08780206,IF(B46=1991,0.10655716,IF(B46=1992,0.1269022,IF(B46=1993,0.13044565,IF(B46=1994,0.0952,IF(B46=1995,0.07845,IF(B46=1996,0.04089,IF(B46=1997,0.06913,IF(B46=1998,0.0873744,""))))))))))))))))))</f>
@@ -33154,7 +33150,7 @@
       <c r="A48" s="503"/>
       <c r="B48" s="504"/>
       <c r="C48" s="505" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D48" s="504"/>
       <c r="E48" s="508">
@@ -33171,7 +33167,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="496" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B50" s="511">
         <f>IF(B46&gt;1997,"",B46+1)</f>
@@ -33179,7 +33175,7 @@
       </c>
       <c r="C50" s="497"/>
       <c r="D50" s="498" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E50" s="499">
         <f>IF(B50=1981,0.055,IF(B50=1982,0.0845,IF(B50=1983,0.1017,IF(B50=1984,0.093807,IF(B50=1985,0.12604006,IF(B50=1986,0.08076508,IF(B50=1987,0.06066944,IF(B50=1988,0.06668109,IF(B50=1989,0.08438409,IF(B50=1990,0.08780206,IF(B50=1991,0.10655716,IF(B50=1992,0.1269022,IF(B50=1993,0.13044565,IF(B50=1994,0.0952,IF(B50=1995,0.07845,IF(B50=1996,0.04089,IF(B50=1997,0.06913,IF(B50=1998,0.0873744,""))))))))))))))))))</f>
@@ -33200,7 +33196,7 @@
       <c r="A52" s="503"/>
       <c r="B52" s="504"/>
       <c r="C52" s="505" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D52" s="504"/>
       <c r="E52" s="508">
@@ -33217,7 +33213,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="496" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B54" s="511">
         <f>IF(B50&gt;1997,"",B50+1)</f>
@@ -33225,7 +33221,7 @@
       </c>
       <c r="C54" s="497"/>
       <c r="D54" s="498" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E54" s="499">
         <f>IF(B54=1981,0.055,IF(B54=1982,0.0845,IF(B54=1983,0.1017,IF(B54=1984,0.093807,IF(B54=1985,0.12604006,IF(B54=1986,0.08076508,IF(B54=1987,0.06066944,IF(B54=1988,0.06668109,IF(B54=1989,0.08438409,IF(B54=1990,0.08780206,IF(B54=1991,0.10655716,IF(B54=1992,0.1269022,IF(B54=1993,0.13044565,IF(B54=1994,0.0952,IF(B54=1995,0.07845,IF(B54=1996,0.04089,IF(B54=1997,0.06913,IF(B54=1998,0.0873744,""))))))))))))))))))</f>
@@ -33246,7 +33242,7 @@
       <c r="A56" s="503"/>
       <c r="B56" s="504"/>
       <c r="C56" s="505" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D56" s="504"/>
       <c r="E56" s="508">
@@ -33263,7 +33259,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="496" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B58" s="511">
         <f>IF(B54&gt;1997,"",B54+1)</f>
@@ -33271,7 +33267,7 @@
       </c>
       <c r="C58" s="497"/>
       <c r="D58" s="498" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E58" s="499">
         <f>IF(B58=1981,0.055,IF(B58=1982,0.0845,IF(B58=1983,0.1017,IF(B58=1984,0.093807,IF(B58=1985,0.12604006,IF(B58=1986,0.08076508,IF(B58=1987,0.06066944,IF(B58=1988,0.06668109,IF(B58=1989,0.08438409,IF(B58=1990,0.08780206,IF(B58=1991,0.10655716,IF(B58=1992,0.1269022,IF(B58=1993,0.13044565,IF(B58=1994,0.0952,IF(B58=1995,0.07845,IF(B58=1996,0.04089,IF(B58=1997,0.06913,IF(B58=1998,0.0873744,""))))))))))))))))))</f>
@@ -33292,7 +33288,7 @@
       <c r="A60" s="503"/>
       <c r="B60" s="504"/>
       <c r="C60" s="505" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D60" s="504"/>
       <c r="E60" s="508">
@@ -33309,7 +33305,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="496" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B62" s="511">
         <f>IF(B58&gt;1997,"",B58+1)</f>
@@ -33317,7 +33313,7 @@
       </c>
       <c r="C62" s="497"/>
       <c r="D62" s="498" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E62" s="499">
         <f>IF(B62=1981,0.055,IF(B62=1982,0.0845,IF(B62=1983,0.1017,IF(B62=1984,0.093807,IF(B62=1985,0.12604006,IF(B62=1986,0.08076508,IF(B62=1987,0.06066944,IF(B62=1988,0.06668109,IF(B62=1989,0.08438409,IF(B62=1990,0.08780206,IF(B62=1991,0.10655716,IF(B62=1992,0.1269022,IF(B62=1993,0.13044565,IF(B62=1994,0.0952,IF(B62=1995,0.07845,IF(B62=1996,0.04089,IF(B62=1997,0.06913,IF(B62=1998,0.0873744,""))))))))))))))))))</f>
@@ -33338,7 +33334,7 @@
       <c r="A64" s="503"/>
       <c r="B64" s="504"/>
       <c r="C64" s="505" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D64" s="504"/>
       <c r="E64" s="506">
@@ -33355,7 +33351,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="496" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B66" s="511">
         <f>IF(B62&gt;1997,"",B62+1)</f>
@@ -33363,7 +33359,7 @@
       </c>
       <c r="C66" s="497"/>
       <c r="D66" s="498" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E66" s="499">
         <f>IF(B66=1981,0.055,IF(B66=1982,0.0845,IF(B66=1983,0.1017,IF(B66=1984,0.093807,IF(B66=1985,0.12604006,IF(B66=1986,0.08076508,IF(B66=1987,0.06066944,IF(B66=1988,0.06668109,IF(B66=1989,0.08438409,IF(B66=1990,0.08780206,IF(B66=1991,0.10655716,IF(B66=1992,0.1269022,IF(B66=1993,0.13044565,IF(B66=1994,0.0952,IF(B66=1995,0.07845,IF(B66=1996,0.04089,IF(B66=1997,0.06913,IF(B66=1998,0.0873744,""))))))))))))))))))</f>
@@ -33384,7 +33380,7 @@
       <c r="A68" s="503"/>
       <c r="B68" s="504"/>
       <c r="C68" s="505" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D68" s="504"/>
       <c r="E68" s="508">
@@ -33401,7 +33397,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="496" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B70" s="511">
         <f>IF(B66&gt;1997,"",B66+1)</f>
@@ -33409,7 +33405,7 @@
       </c>
       <c r="C70" s="497"/>
       <c r="D70" s="498" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E70" s="499">
         <f>IF(B70=1981,0.055,IF(B70=1982,0.0845,IF(B70=1983,0.1017,IF(B70=1984,0.093807,IF(B70=1985,0.12604006,IF(B70=1986,0.08076508,IF(B70=1987,0.06066944,IF(B70=1988,0.06668109,IF(B70=1989,0.08438409,IF(B70=1990,0.08780206,IF(B70=1991,0.10655716,IF(B70=1992,0.1269022,IF(B70=1993,0.13044565,IF(B70=1994,0.0952,IF(B70=1995,0.07845,IF(B70=1996,0.04089,IF(B70=1997,0.06913,IF(B70=1998,0.0873744,""))))))))))))))))))</f>
@@ -33430,7 +33426,7 @@
       <c r="A72" s="503"/>
       <c r="B72" s="504"/>
       <c r="C72" s="505" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D72" s="504"/>
       <c r="E72" s="508">
@@ -33447,7 +33443,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="496" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B74" s="511">
         <f>IF(B70&gt;1997,"",B70+1)</f>
@@ -33455,7 +33451,7 @@
       </c>
       <c r="C74" s="497"/>
       <c r="D74" s="498" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E74" s="499">
         <f>IF(B74=1981,0.055,IF(B74=1982,0.0845,IF(B74=1983,0.1017,IF(B74=1984,0.093807,IF(B74=1985,0.12604006,IF(B74=1986,0.08076508,IF(B74=1987,0.06066944,IF(B74=1988,0.06668109,IF(B74=1989,0.08438409,IF(B74=1990,0.08780206,IF(B74=1991,0.10655716,IF(B74=1992,0.1269022,IF(B74=1993,0.13044565,IF(B74=1994,0.0952,IF(B74=1995,0.07845,IF(B74=1996,0.04089,IF(B74=1997,0.06913,IF(B74=1998,0.0873744,""))))))))))))))))))</f>
@@ -33476,7 +33472,7 @@
       <c r="A76" s="503"/>
       <c r="B76" s="504"/>
       <c r="C76" s="505" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D76" s="504"/>
       <c r="E76" s="508">
@@ -33493,7 +33489,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="496" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B78" s="511">
         <f>IF(B74&gt;1997,"",B74+1)</f>
@@ -33501,7 +33497,7 @@
       </c>
       <c r="C78" s="497"/>
       <c r="D78" s="498" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E78" s="499">
         <f>IF(B78=1981,0.055,IF(B78=1982,0.0845,IF(B78=1983,0.1017,IF(B78=1984,0.093807,IF(B78=1985,0.12604006,IF(B78=1986,0.08076508,IF(B78=1987,0.06066944,IF(B78=1988,0.06668109,IF(B78=1989,0.08438409,IF(B78=1990,0.08780206,IF(B78=1991,0.10655716,IF(B78=1992,0.1269022,IF(B78=1993,0.13044565,IF(B78=1994,0.0952,IF(B78=1995,0.07845,IF(B78=1996,0.04089,IF(B78=1997,0.06913,IF(B78=1998,0.0873744,""))))))))))))))))))</f>
@@ -33522,7 +33518,7 @@
       <c r="A80" s="503"/>
       <c r="B80" s="504"/>
       <c r="C80" s="505" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D80" s="504"/>
       <c r="E80" s="508">
@@ -33539,7 +33535,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="496" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B82" s="511" t="str">
         <f>IF(B78&gt;1997,"",B78+1)</f>
@@ -33547,7 +33543,7 @@
       </c>
       <c r="C82" s="497"/>
       <c r="D82" s="498" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E82" s="499" t="str">
         <f>IF(B82=1981,0.055,IF(B82=1982,0.0845,IF(B82=1983,0.1017,IF(B82=1984,0.093807,IF(B82=1985,0.12604006,IF(B82=1986,0.08076508,IF(B82=1987,0.06066944,IF(B82=1988,0.06668109,IF(B82=1989,0.08438409,IF(B82=1990,0.08780206,IF(B82=1991,0.10655716,IF(B82=1992,0.1269022,IF(B82=1993,0.13044565,IF(B82=1994,0.0952,IF(B82=1995,0.07845,IF(B82=1996,0.04089,IF(B82=1997,0.06913,IF(B82=1998,0.0873744,""))))))))))))))))))</f>
@@ -33568,7 +33564,7 @@
       <c r="A84" s="503"/>
       <c r="B84" s="504"/>
       <c r="C84" s="505" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D84" s="504"/>
       <c r="E84" s="508" t="e">
@@ -33585,7 +33581,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="496" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B86" s="511" t="str">
         <f>IF(B82&gt;1997,"",B82+1)</f>
@@ -33593,7 +33589,7 @@
       </c>
       <c r="C86" s="497"/>
       <c r="D86" s="498" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E86" s="499" t="str">
         <f>IF(B86=1981,0.055,IF(B86=1982,0.0845,IF(B86=1983,0.1017,IF(B86=1984,0.093807,IF(B86=1985,0.12604006,IF(B86=1986,0.08076508,IF(B86=1987,0.06066944,IF(B86=1988,0.06668109,IF(B86=1989,0.08438409,IF(B86=1990,0.08780206,IF(B86=1991,0.10655716,IF(B86=1992,0.1269022,IF(B86=1993,0.13044565,IF(B86=1994,0.0952,IF(B86=1995,0.07845,IF(B86=1996,0.04089,IF(B86=1997,0.06913,IF(B86=1998,0.0873744,""))))))))))))))))))</f>
@@ -33614,7 +33610,7 @@
       <c r="A88" s="503"/>
       <c r="B88" s="504"/>
       <c r="C88" s="505" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D88" s="504"/>
       <c r="E88" s="508" t="e">
@@ -33631,7 +33627,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" s="496" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B90" s="511" t="str">
         <f>IF(B86&gt;1997,"",B86+1)</f>
@@ -33639,7 +33635,7 @@
       </c>
       <c r="C90" s="497"/>
       <c r="D90" s="498" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E90" s="499" t="str">
         <f>IF(B90=1981,0.055,IF(B90=1982,0.0845,IF(B90=1983,0.1017,IF(B90=1984,0.093807,IF(B90=1985,0.12604006,IF(B90=1986,0.08076508,IF(B90=1987,0.06066944,IF(B90=1988,0.06668109,IF(B90=1989,0.08438409,IF(B90=1990,0.08780206,IF(B90=1991,0.10655716,IF(B90=1992,0.1269022,IF(B90=1993,0.13044565,IF(B90=1994,0.0952,IF(B90=1995,0.07845,IF(B90=1996,0.04089,IF(B90=1997,0.06913,IF(B90=1998,0.0873744,""))))))))))))))))))</f>
@@ -33660,7 +33656,7 @@
       <c r="A92" s="503"/>
       <c r="B92" s="504"/>
       <c r="C92" s="505" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D92" s="504"/>
       <c r="E92" s="508" t="e">
@@ -33677,7 +33673,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" s="496" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B94" s="511" t="str">
         <f>IF(B90&gt;1997,"",B90+1)</f>
@@ -33685,7 +33681,7 @@
       </c>
       <c r="C94" s="497"/>
       <c r="D94" s="498" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E94" s="499" t="str">
         <f>IF(B94=1981,0.055,IF(B94=1982,0.0845,IF(B94=1983,0.1017,IF(B94=1984,0.093807,IF(B94=1985,0.12604006,IF(B94=1986,0.08076508,IF(B94=1987,0.06066944,IF(B94=1988,0.06668109,IF(B94=1989,0.08438409,IF(B94=1990,0.08780206,IF(B94=1991,0.10655716,IF(B94=1992,0.1269022,IF(B94=1993,0.13044565,IF(B94=1994,0.0952,IF(B94=1995,0.07845,IF(B94=1996,0.04089,IF(B94=1997,0.06913,IF(B94=1998,0.0873744,""))))))))))))))))))</f>
@@ -33706,7 +33702,7 @@
       <c r="A96" s="503"/>
       <c r="B96" s="504"/>
       <c r="C96" s="505" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D96" s="504"/>
       <c r="E96" s="508" t="e">
